--- a/templates/productie/productie_grondwater_template.xlsx
+++ b/templates/productie/productie_grondwater_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9246" uniqueCount="2064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9245" uniqueCount="2065">
   <si>
     <t>identificatie</t>
   </si>
@@ -4196,6 +4196,9 @@
     <t>Andere referentiepunt</t>
   </si>
   <si>
+    <t>Bovenkant straatpot</t>
+  </si>
+  <si>
     <t>filtermeting</t>
   </si>
   <si>
@@ -6182,25 +6185,25 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-02-10 16:30:52.282032</t>
+    <t>2026-03-31 16:50:29.723209</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.2.3</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>9.4.3</t>
+    <t>10.1.0</t>
   </si>
   <si>
     <t>schema-version</t>
   </si>
   <si>
-    <t>5.9.0</t>
+    <t>5.10.0</t>
   </si>
   <si>
     <t>mode</t>
@@ -6407,7 +6410,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table17" displayName="Table17" ref="AG3:AH8" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Table17" displayName="Table17" ref="AG3:AH9" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -7025,7 +7028,7 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -7049,7 +7052,7 @@
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
@@ -7157,59 +7160,59 @@
       </c>
       <c r="AH2" s="1"/>
       <c r="AI2" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="AJ2" s="1"/>
       <c r="AK2" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="AN2" s="1"/>
       <c r="AO2" s="1" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="AP2" s="1"/>
       <c r="AQ2" s="1" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="AR2" s="1"/>
       <c r="AS2" s="1" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="AT2" s="1"/>
       <c r="AU2" s="1" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1" t="s">
@@ -7221,7 +7224,7 @@
       </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1" t="s">
@@ -7229,15 +7232,15 @@
       </c>
       <c r="BR2" s="1"/>
       <c r="BS2" s="1" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="BT2" s="1"/>
       <c r="BU2" s="1" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="BV2" s="1"/>
       <c r="BW2" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BX2" s="1"/>
     </row>
@@ -7575,19 +7578,19 @@
         <v>33</v>
       </c>
       <c r="AI4" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="AJ4" t="s">
         <v>33</v>
       </c>
       <c r="AK4" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="AL4" t="s">
         <v>33</v>
       </c>
       <c r="AM4" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="AN4" t="s">
         <v>33</v>
@@ -7605,31 +7608,31 @@
         <v>33</v>
       </c>
       <c r="AS4" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="AT4" t="s">
         <v>33</v>
       </c>
       <c r="AU4" s="2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="AV4" t="s">
         <v>33</v>
       </c>
       <c r="AW4" s="2" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="AX4" t="s">
         <v>33</v>
       </c>
       <c r="AY4" s="2" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="AZ4" t="s">
         <v>33</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="BB4" t="s">
         <v>33</v>
@@ -7671,13 +7674,13 @@
         <v>33</v>
       </c>
       <c r="BO4" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="BP4" t="s">
         <v>33</v>
       </c>
       <c r="BQ4" s="2" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="BR4" t="s">
         <v>33</v>
@@ -7805,67 +7808,67 @@
         <v>33</v>
       </c>
       <c r="AI5" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="AJ5" t="s">
         <v>33</v>
       </c>
       <c r="AK5" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="AL5" t="s">
         <v>33</v>
       </c>
       <c r="AM5" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="AN5" t="s">
         <v>33</v>
       </c>
       <c r="AO5" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="AP5" t="s">
         <v>33</v>
       </c>
       <c r="AQ5" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="AR5" t="s">
         <v>33</v>
       </c>
       <c r="AS5" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="AT5" t="s">
         <v>33</v>
       </c>
       <c r="AU5" s="2" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="AV5" t="s">
         <v>33</v>
       </c>
       <c r="AW5" s="2" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="AX5" t="s">
         <v>33</v>
       </c>
       <c r="AY5" s="2" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="AZ5" t="s">
         <v>33</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="BB5" t="s">
         <v>33</v>
       </c>
       <c r="BC5" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="BD5" t="s">
         <v>33</v>
@@ -7901,13 +7904,13 @@
         <v>33</v>
       </c>
       <c r="BO5" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="BP5" t="s">
         <v>33</v>
       </c>
       <c r="BQ5" s="2" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="BR5" t="s">
         <v>33</v>
@@ -7925,7 +7928,7 @@
         <v>33</v>
       </c>
       <c r="BW5" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="BX5" t="s">
         <v>33</v>
@@ -8023,61 +8026,61 @@
         <v>33</v>
       </c>
       <c r="AI6" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="AJ6" t="s">
         <v>33</v>
       </c>
       <c r="AK6" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="AL6" t="s">
         <v>33</v>
       </c>
       <c r="AM6" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="AN6" t="s">
         <v>33</v>
       </c>
       <c r="AO6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="AP6" t="s">
         <v>33</v>
       </c>
       <c r="AQ6" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="AR6" t="s">
         <v>33</v>
       </c>
       <c r="AU6" s="2" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="AV6" t="s">
         <v>33</v>
       </c>
       <c r="AW6" s="2" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="AX6" t="s">
         <v>33</v>
       </c>
       <c r="AY6" s="2" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="AZ6" t="s">
         <v>33</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="BB6" t="s">
         <v>33</v>
       </c>
       <c r="BC6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="BD6" t="s">
         <v>33</v>
@@ -8113,13 +8116,13 @@
         <v>33</v>
       </c>
       <c r="BO6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="BP6" t="s">
         <v>33</v>
       </c>
       <c r="BQ6" s="2" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="BR6" t="s">
         <v>33</v>
@@ -8137,7 +8140,7 @@
         <v>33</v>
       </c>
       <c r="BW6" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="BX6" t="s">
         <v>33</v>
@@ -8217,55 +8220,55 @@
         <v>33</v>
       </c>
       <c r="AI7" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="AJ7" t="s">
         <v>33</v>
       </c>
       <c r="AK7" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="AL7" t="s">
         <v>33</v>
       </c>
       <c r="AM7" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="AN7" t="s">
         <v>33</v>
       </c>
       <c r="AO7" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="AP7" t="s">
         <v>33</v>
       </c>
       <c r="AQ7" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="AR7" t="s">
         <v>33</v>
       </c>
       <c r="AU7" s="2" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="AV7" t="s">
         <v>33</v>
       </c>
       <c r="AW7" s="2" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="AX7" t="s">
         <v>33</v>
       </c>
       <c r="AY7" s="2" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="AZ7" t="s">
         <v>33</v>
       </c>
       <c r="BC7" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="BD7" t="s">
         <v>33</v>
@@ -8295,7 +8298,7 @@
         <v>33</v>
       </c>
       <c r="BO7" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="BP7" t="s">
         <v>33</v>
@@ -8313,7 +8316,7 @@
         <v>33</v>
       </c>
       <c r="BW7" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="BX7" t="s">
         <v>33</v>
@@ -8387,55 +8390,55 @@
         <v>33</v>
       </c>
       <c r="AI8" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="AJ8" t="s">
         <v>33</v>
       </c>
       <c r="AK8" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="AL8" t="s">
         <v>33</v>
       </c>
       <c r="AM8" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="AN8" t="s">
         <v>33</v>
       </c>
       <c r="AO8" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="AP8" t="s">
         <v>33</v>
       </c>
       <c r="AQ8" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="AR8" t="s">
         <v>33</v>
       </c>
       <c r="AU8" s="2" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="AV8" t="s">
         <v>33</v>
       </c>
       <c r="AW8" s="2" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="AX8" t="s">
         <v>33</v>
       </c>
       <c r="AY8" s="2" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="AZ8" t="s">
         <v>33</v>
       </c>
       <c r="BC8" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="BD8" t="s">
         <v>33</v>
@@ -8465,7 +8468,7 @@
         <v>33</v>
       </c>
       <c r="BO8" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="BP8" t="s">
         <v>33</v>
@@ -8483,7 +8486,7 @@
         <v>33</v>
       </c>
       <c r="BW8" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="BX8" t="s">
         <v>33</v>
@@ -8550,50 +8553,56 @@
       <c r="AF9" t="s">
         <v>33</v>
       </c>
+      <c r="AG9" t="s">
+        <v>1391</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>33</v>
+      </c>
       <c r="AI9" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="AJ9" t="s">
         <v>33</v>
       </c>
       <c r="AK9" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="AL9" t="s">
         <v>33</v>
       </c>
       <c r="AO9" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="AP9" t="s">
         <v>33</v>
       </c>
       <c r="AQ9" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="AR9" t="s">
         <v>33</v>
       </c>
       <c r="AU9" s="2" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="AV9" t="s">
         <v>33</v>
       </c>
       <c r="AW9" s="2" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="AX9" t="s">
         <v>33</v>
       </c>
       <c r="AY9" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="AZ9" t="s">
         <v>33</v>
       </c>
       <c r="BC9" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="BD9" t="s">
         <v>33</v>
@@ -8623,7 +8632,7 @@
         <v>33</v>
       </c>
       <c r="BO9" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="BP9" t="s">
         <v>33</v>
@@ -8641,7 +8650,7 @@
         <v>33</v>
       </c>
       <c r="BW9" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="BX9" t="s">
         <v>33</v>
@@ -8709,49 +8718,49 @@
         <v>33</v>
       </c>
       <c r="AI10" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="AJ10" t="s">
         <v>33</v>
       </c>
       <c r="AK10" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="AL10" t="s">
         <v>33</v>
       </c>
       <c r="AO10" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="AP10" t="s">
         <v>33</v>
       </c>
       <c r="AQ10" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
       <c r="AU10" s="2" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="AV10" t="s">
         <v>33</v>
       </c>
       <c r="AW10" s="2" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="AX10" t="s">
         <v>33</v>
       </c>
       <c r="AY10" s="2" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="AZ10" t="s">
         <v>33</v>
       </c>
       <c r="BC10" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="BD10" t="s">
         <v>33</v>
@@ -8781,7 +8790,7 @@
         <v>33</v>
       </c>
       <c r="BO10" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="BP10" t="s">
         <v>33</v>
@@ -8799,7 +8808,7 @@
         <v>33</v>
       </c>
       <c r="BW10" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="BX10" t="s">
         <v>33</v>
@@ -8849,49 +8858,49 @@
         <v>33</v>
       </c>
       <c r="AI11" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="AJ11" t="s">
         <v>33</v>
       </c>
       <c r="AK11" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="AL11" t="s">
         <v>33</v>
       </c>
       <c r="AO11" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="AP11" t="s">
         <v>33</v>
       </c>
       <c r="AQ11" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="AR11" t="s">
         <v>33</v>
       </c>
       <c r="AU11" s="2" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="AV11" t="s">
         <v>33</v>
       </c>
       <c r="AW11" s="2" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="AX11" t="s">
         <v>33</v>
       </c>
       <c r="AY11" s="2" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="AZ11" t="s">
         <v>33</v>
       </c>
       <c r="BC11" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="BD11" t="s">
         <v>33</v>
@@ -8921,7 +8930,7 @@
         <v>33</v>
       </c>
       <c r="BO11" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="BP11" t="s">
         <v>33</v>
@@ -8939,7 +8948,7 @@
         <v>33</v>
       </c>
       <c r="BW11" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="BX11" t="s">
         <v>33</v>
@@ -8989,49 +8998,49 @@
         <v>33</v>
       </c>
       <c r="AI12" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="AJ12" t="s">
         <v>33</v>
       </c>
       <c r="AK12" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="AL12" t="s">
         <v>33</v>
       </c>
       <c r="AO12" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="AP12" t="s">
         <v>33</v>
       </c>
       <c r="AQ12" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="AR12" t="s">
         <v>33</v>
       </c>
       <c r="AU12" s="2" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="AV12" t="s">
         <v>33</v>
       </c>
       <c r="AW12" s="2" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="AX12" t="s">
         <v>33</v>
       </c>
       <c r="AY12" s="2" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AZ12" t="s">
         <v>33</v>
       </c>
       <c r="BC12" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="BD12" t="s">
         <v>33</v>
@@ -9061,7 +9070,7 @@
         <v>33</v>
       </c>
       <c r="BO12" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="BP12" t="s">
         <v>33</v>
@@ -9079,7 +9088,7 @@
         <v>33</v>
       </c>
       <c r="BW12" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="BX12" t="s">
         <v>33</v>
@@ -9129,43 +9138,43 @@
         <v>33</v>
       </c>
       <c r="AI13" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="AJ13" t="s">
         <v>33</v>
       </c>
       <c r="AK13" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="AL13" t="s">
         <v>33</v>
       </c>
       <c r="AO13" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AP13" t="s">
         <v>33</v>
       </c>
       <c r="AQ13" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="AR13" t="s">
         <v>33</v>
       </c>
       <c r="AU13" s="2" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="AV13" t="s">
         <v>33</v>
       </c>
       <c r="AY13" s="2" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="AZ13" t="s">
         <v>33</v>
       </c>
       <c r="BC13" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="BD13" t="s">
         <v>33</v>
@@ -9195,7 +9204,7 @@
         <v>33</v>
       </c>
       <c r="BO13" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="BP13" t="s">
         <v>33</v>
@@ -9213,7 +9222,7 @@
         <v>33</v>
       </c>
       <c r="BW13" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="BX13" t="s">
         <v>33</v>
@@ -9263,43 +9272,43 @@
         <v>33</v>
       </c>
       <c r="AI14" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="AJ14" t="s">
         <v>33</v>
       </c>
       <c r="AK14" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="AL14" t="s">
         <v>33</v>
       </c>
       <c r="AO14" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="AP14" t="s">
         <v>33</v>
       </c>
       <c r="AQ14" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="AR14" t="s">
         <v>33</v>
       </c>
       <c r="AU14" s="2" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="AV14" t="s">
         <v>33</v>
       </c>
       <c r="AY14" s="2" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="AZ14" t="s">
         <v>33</v>
       </c>
       <c r="BC14" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="BD14" t="s">
         <v>33</v>
@@ -9329,7 +9338,7 @@
         <v>33</v>
       </c>
       <c r="BO14" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="BP14" t="s">
         <v>33</v>
@@ -9347,7 +9356,7 @@
         <v>33</v>
       </c>
       <c r="BW14" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="BX14" t="s">
         <v>33</v>
@@ -9397,43 +9406,43 @@
         <v>33</v>
       </c>
       <c r="AI15" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="AJ15" t="s">
         <v>33</v>
       </c>
       <c r="AK15" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="AL15" t="s">
         <v>33</v>
       </c>
       <c r="AO15" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="AP15" t="s">
         <v>33</v>
       </c>
       <c r="AQ15" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="AR15" t="s">
         <v>33</v>
       </c>
       <c r="AU15" s="2" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="AV15" t="s">
         <v>33</v>
       </c>
       <c r="AY15" s="2" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="AZ15" t="s">
         <v>33</v>
       </c>
       <c r="BC15" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="BD15" t="s">
         <v>33</v>
@@ -9463,7 +9472,7 @@
         <v>33</v>
       </c>
       <c r="BO15" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="BP15" t="s">
         <v>33</v>
@@ -9481,7 +9490,7 @@
         <v>33</v>
       </c>
       <c r="BW15" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="BX15" t="s">
         <v>33</v>
@@ -9531,43 +9540,43 @@
         <v>33</v>
       </c>
       <c r="AI16" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="AJ16" t="s">
         <v>33</v>
       </c>
       <c r="AK16" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="AL16" t="s">
         <v>33</v>
       </c>
       <c r="AO16" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="AP16" t="s">
         <v>33</v>
       </c>
       <c r="AQ16" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="AR16" t="s">
         <v>33</v>
       </c>
       <c r="AU16" s="2" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="AV16" t="s">
         <v>33</v>
       </c>
       <c r="AY16" s="2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="AZ16" t="s">
         <v>33</v>
       </c>
       <c r="BC16" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="BD16" t="s">
         <v>33</v>
@@ -9597,7 +9606,7 @@
         <v>33</v>
       </c>
       <c r="BO16" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="BP16" t="s">
         <v>33</v>
@@ -9615,7 +9624,7 @@
         <v>33</v>
       </c>
       <c r="BW16" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="BX16" t="s">
         <v>33</v>
@@ -9659,43 +9668,43 @@
         <v>33</v>
       </c>
       <c r="AI17" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="AJ17" t="s">
         <v>33</v>
       </c>
       <c r="AK17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="AL17" t="s">
         <v>33</v>
       </c>
       <c r="AO17" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="AP17" t="s">
         <v>33</v>
       </c>
       <c r="AQ17" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="AR17" t="s">
         <v>33</v>
       </c>
       <c r="AU17" s="2" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="AV17" t="s">
         <v>33</v>
       </c>
       <c r="AY17" s="2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="AZ17" t="s">
         <v>33</v>
       </c>
       <c r="BC17" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="BD17" t="s">
         <v>33</v>
@@ -9725,7 +9734,7 @@
         <v>33</v>
       </c>
       <c r="BO17" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="BP17" t="s">
         <v>33</v>
@@ -9743,7 +9752,7 @@
         <v>33</v>
       </c>
       <c r="BW17" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="BX17" t="s">
         <v>33</v>
@@ -9781,43 +9790,43 @@
         <v>33</v>
       </c>
       <c r="AI18" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="AJ18" t="s">
         <v>33</v>
       </c>
       <c r="AK18" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="AL18" t="s">
         <v>33</v>
       </c>
       <c r="AO18" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="AP18" t="s">
         <v>33</v>
       </c>
       <c r="AQ18" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="AR18" t="s">
         <v>33</v>
       </c>
       <c r="AU18" s="2" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="AV18" t="s">
         <v>33</v>
       </c>
       <c r="AY18" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="AZ18" t="s">
         <v>33</v>
       </c>
       <c r="BC18" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="BD18" t="s">
         <v>33</v>
@@ -9847,7 +9856,7 @@
         <v>33</v>
       </c>
       <c r="BO18" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="BP18" t="s">
         <v>33</v>
@@ -9865,7 +9874,7 @@
         <v>33</v>
       </c>
       <c r="BW18" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="BX18" t="s">
         <v>33</v>
@@ -9897,37 +9906,37 @@
         <v>33</v>
       </c>
       <c r="AI19" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="AJ19" t="s">
         <v>33</v>
       </c>
       <c r="AO19" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="AP19" t="s">
         <v>33</v>
       </c>
       <c r="AQ19" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="AR19" t="s">
         <v>33</v>
       </c>
       <c r="AU19" s="2" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="AV19" t="s">
         <v>33</v>
       </c>
       <c r="AY19" s="2" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="AZ19" t="s">
         <v>33</v>
       </c>
       <c r="BC19" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="BD19" t="s">
         <v>33</v>
@@ -9975,7 +9984,7 @@
         <v>33</v>
       </c>
       <c r="BW19" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="BX19" t="s">
         <v>33</v>
@@ -10007,37 +10016,37 @@
         <v>33</v>
       </c>
       <c r="AI20" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="AJ20" t="s">
         <v>33</v>
       </c>
       <c r="AO20" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="AP20" t="s">
         <v>33</v>
       </c>
       <c r="AQ20" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="AR20" t="s">
         <v>33</v>
       </c>
       <c r="AU20" s="2" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="AV20" t="s">
         <v>33</v>
       </c>
       <c r="AY20" s="2" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="AZ20" t="s">
         <v>33</v>
       </c>
       <c r="BC20" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="BD20" t="s">
         <v>33</v>
@@ -10067,7 +10076,7 @@
         <v>33</v>
       </c>
       <c r="BO20" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="BP20" t="s">
         <v>33</v>
@@ -10085,7 +10094,7 @@
         <v>33</v>
       </c>
       <c r="BW20" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="BX20" t="s">
         <v>33</v>
@@ -10111,37 +10120,37 @@
         <v>33</v>
       </c>
       <c r="AI21" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="AJ21" t="s">
         <v>33</v>
       </c>
       <c r="AO21" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="AP21" t="s">
         <v>33</v>
       </c>
       <c r="AQ21" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="AR21" t="s">
         <v>33</v>
       </c>
       <c r="AU21" s="2" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="AV21" t="s">
         <v>33</v>
       </c>
       <c r="AY21" s="2" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="AZ21" t="s">
         <v>33</v>
       </c>
       <c r="BC21" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="BD21" t="s">
         <v>33</v>
@@ -10171,7 +10180,7 @@
         <v>33</v>
       </c>
       <c r="BO21" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="BP21" t="s">
         <v>33</v>
@@ -10189,7 +10198,7 @@
         <v>33</v>
       </c>
       <c r="BW21" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="BX21" t="s">
         <v>33</v>
@@ -10215,37 +10224,37 @@
         <v>33</v>
       </c>
       <c r="AI22" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="AJ22" t="s">
         <v>33</v>
       </c>
       <c r="AO22" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="AP22" t="s">
         <v>33</v>
       </c>
       <c r="AQ22" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="AR22" t="s">
         <v>33</v>
       </c>
       <c r="AU22" s="2" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="AV22" t="s">
         <v>33</v>
       </c>
       <c r="AY22" s="2" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="AZ22" t="s">
         <v>33</v>
       </c>
       <c r="BC22" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="BD22" t="s">
         <v>33</v>
@@ -10275,7 +10284,7 @@
         <v>33</v>
       </c>
       <c r="BO22" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="BP22" t="s">
         <v>33</v>
@@ -10293,7 +10302,7 @@
         <v>33</v>
       </c>
       <c r="BW22" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="BX22" t="s">
         <v>33</v>
@@ -10319,37 +10328,37 @@
         <v>33</v>
       </c>
       <c r="AI23" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="AJ23" t="s">
         <v>33</v>
       </c>
       <c r="AO23" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="AP23" t="s">
         <v>33</v>
       </c>
       <c r="AQ23" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="AR23" t="s">
         <v>33</v>
       </c>
       <c r="AU23" s="2" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="AV23" t="s">
         <v>33</v>
       </c>
       <c r="AY23" s="2" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="AZ23" t="s">
         <v>33</v>
       </c>
       <c r="BC23" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="BD23" t="s">
         <v>33</v>
@@ -10379,7 +10388,7 @@
         <v>33</v>
       </c>
       <c r="BO23" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="BP23" t="s">
         <v>33</v>
@@ -10397,7 +10406,7 @@
         <v>33</v>
       </c>
       <c r="BW23" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="BX23" t="s">
         <v>33</v>
@@ -10423,31 +10432,31 @@
         <v>33</v>
       </c>
       <c r="AI24" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="AJ24" t="s">
         <v>33</v>
       </c>
       <c r="AO24" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="AP24" t="s">
         <v>33</v>
       </c>
       <c r="AU24" s="2" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="AV24" t="s">
         <v>33</v>
       </c>
       <c r="AY24" s="2" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="AZ24" t="s">
         <v>33</v>
       </c>
       <c r="BC24" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="BD24" t="s">
         <v>33</v>
@@ -10477,7 +10486,7 @@
         <v>33</v>
       </c>
       <c r="BO24" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="BP24" t="s">
         <v>33</v>
@@ -10495,7 +10504,7 @@
         <v>33</v>
       </c>
       <c r="BW24" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="BX24" t="s">
         <v>33</v>
@@ -10521,31 +10530,31 @@
         <v>33</v>
       </c>
       <c r="AI25" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="AJ25" t="s">
         <v>33</v>
       </c>
       <c r="AO25" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="AP25" t="s">
         <v>33</v>
       </c>
       <c r="AU25" s="2" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="AV25" t="s">
         <v>33</v>
       </c>
       <c r="AY25" s="2" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="AZ25" t="s">
         <v>33</v>
       </c>
       <c r="BC25" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="BD25" t="s">
         <v>33</v>
@@ -10575,7 +10584,7 @@
         <v>33</v>
       </c>
       <c r="BO25" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="BP25" t="s">
         <v>33</v>
@@ -10593,7 +10602,7 @@
         <v>33</v>
       </c>
       <c r="BW25" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="BX25" t="s">
         <v>33</v>
@@ -10619,31 +10628,31 @@
         <v>33</v>
       </c>
       <c r="AI26" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="AJ26" t="s">
         <v>33</v>
       </c>
       <c r="AO26" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="AP26" t="s">
         <v>33</v>
       </c>
       <c r="AU26" s="2" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="AV26" t="s">
         <v>33</v>
       </c>
       <c r="AY26" s="2" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="AZ26" t="s">
         <v>33</v>
       </c>
       <c r="BC26" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="BD26" t="s">
         <v>33</v>
@@ -10673,7 +10682,7 @@
         <v>33</v>
       </c>
       <c r="BO26" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="BP26" t="s">
         <v>33</v>
@@ -10691,7 +10700,7 @@
         <v>33</v>
       </c>
       <c r="BW26" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="BX26" t="s">
         <v>33</v>
@@ -10717,31 +10726,31 @@
         <v>33</v>
       </c>
       <c r="AI27" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="AJ27" t="s">
         <v>33</v>
       </c>
       <c r="AO27" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="AP27" t="s">
         <v>33</v>
       </c>
       <c r="AU27" s="2" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="AV27" t="s">
         <v>33</v>
       </c>
       <c r="AY27" s="2" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="AZ27" t="s">
         <v>33</v>
       </c>
       <c r="BC27" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="BD27" t="s">
         <v>33</v>
@@ -10771,7 +10780,7 @@
         <v>33</v>
       </c>
       <c r="BO27" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="BP27" t="s">
         <v>33</v>
@@ -10789,7 +10798,7 @@
         <v>33</v>
       </c>
       <c r="BW27" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="BX27" t="s">
         <v>33</v>
@@ -10815,31 +10824,31 @@
         <v>33</v>
       </c>
       <c r="AI28" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="AJ28" t="s">
         <v>33</v>
       </c>
       <c r="AO28" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="AP28" t="s">
         <v>33</v>
       </c>
       <c r="AU28" s="2" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="AV28" t="s">
         <v>33</v>
       </c>
       <c r="AY28" s="2" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="AZ28" t="s">
         <v>33</v>
       </c>
       <c r="BC28" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="BD28" t="s">
         <v>33</v>
@@ -10869,7 +10878,7 @@
         <v>33</v>
       </c>
       <c r="BO28" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="BP28" t="s">
         <v>33</v>
@@ -10887,7 +10896,7 @@
         <v>33</v>
       </c>
       <c r="BW28" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="BX28" t="s">
         <v>33</v>
@@ -10913,31 +10922,31 @@
         <v>33</v>
       </c>
       <c r="AI29" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="AJ29" t="s">
         <v>33</v>
       </c>
       <c r="AO29" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="AP29" t="s">
         <v>33</v>
       </c>
       <c r="AU29" s="2" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="AV29" t="s">
         <v>33</v>
       </c>
       <c r="AY29" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="AZ29" t="s">
         <v>33</v>
       </c>
       <c r="BC29" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="BD29" t="s">
         <v>33</v>
@@ -10967,7 +10976,7 @@
         <v>33</v>
       </c>
       <c r="BO29" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="BP29" t="s">
         <v>33</v>
@@ -10985,7 +10994,7 @@
         <v>33</v>
       </c>
       <c r="BW29" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="BX29" t="s">
         <v>33</v>
@@ -11011,25 +11020,25 @@
         <v>33</v>
       </c>
       <c r="AO30" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="AP30" t="s">
         <v>33</v>
       </c>
       <c r="AU30" s="2" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="AV30" t="s">
         <v>33</v>
       </c>
       <c r="AY30" s="2" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="AZ30" t="s">
         <v>33</v>
       </c>
       <c r="BC30" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="BD30" t="s">
         <v>33</v>
@@ -11059,7 +11068,7 @@
         <v>33</v>
       </c>
       <c r="BO30" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="BP30" t="s">
         <v>33</v>
@@ -11077,7 +11086,7 @@
         <v>33</v>
       </c>
       <c r="BW30" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="BX30" t="s">
         <v>33</v>
@@ -11103,25 +11112,25 @@
         <v>33</v>
       </c>
       <c r="AO31" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="AP31" t="s">
         <v>33</v>
       </c>
       <c r="AU31" s="2" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="AV31" t="s">
         <v>33</v>
       </c>
       <c r="AY31" s="2" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="AZ31" t="s">
         <v>33</v>
       </c>
       <c r="BC31" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="BD31" t="s">
         <v>33</v>
@@ -11151,7 +11160,7 @@
         <v>33</v>
       </c>
       <c r="BO31" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="BP31" t="s">
         <v>33</v>
@@ -11169,7 +11178,7 @@
         <v>33</v>
       </c>
       <c r="BW31" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="BX31" t="s">
         <v>33</v>
@@ -11195,25 +11204,25 @@
         <v>33</v>
       </c>
       <c r="AO32" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="AP32" t="s">
         <v>33</v>
       </c>
       <c r="AU32" s="2" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="AV32" t="s">
         <v>33</v>
       </c>
       <c r="AY32" s="2" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="AZ32" t="s">
         <v>33</v>
       </c>
       <c r="BC32" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="BD32" t="s">
         <v>33</v>
@@ -11243,7 +11252,7 @@
         <v>33</v>
       </c>
       <c r="BO32" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="BP32" t="s">
         <v>33</v>
@@ -11261,7 +11270,7 @@
         <v>33</v>
       </c>
       <c r="BW32" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="BX32" t="s">
         <v>33</v>
@@ -11287,25 +11296,25 @@
         <v>33</v>
       </c>
       <c r="AO33" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="AP33" t="s">
         <v>33</v>
       </c>
       <c r="AU33" s="2" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="AV33" t="s">
         <v>33</v>
       </c>
       <c r="AY33" s="2" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AZ33" t="s">
         <v>33</v>
       </c>
       <c r="BC33" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="BD33" t="s">
         <v>33</v>
@@ -11335,7 +11344,7 @@
         <v>33</v>
       </c>
       <c r="BO33" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="BP33" t="s">
         <v>33</v>
@@ -11353,7 +11362,7 @@
         <v>33</v>
       </c>
       <c r="BW33" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="BX33" t="s">
         <v>33</v>
@@ -11379,25 +11388,25 @@
         <v>33</v>
       </c>
       <c r="AO34" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="AP34" t="s">
         <v>33</v>
       </c>
       <c r="AU34" s="2" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="AV34" t="s">
         <v>33</v>
       </c>
       <c r="AY34" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="AZ34" t="s">
         <v>33</v>
       </c>
       <c r="BC34" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="BD34" t="s">
         <v>33</v>
@@ -11427,7 +11436,7 @@
         <v>33</v>
       </c>
       <c r="BO34" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="BP34" t="s">
         <v>33</v>
@@ -11445,7 +11454,7 @@
         <v>33</v>
       </c>
       <c r="BW34" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="BX34" t="s">
         <v>33</v>
@@ -11471,25 +11480,25 @@
         <v>33</v>
       </c>
       <c r="AO35" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="AP35" t="s">
         <v>33</v>
       </c>
       <c r="AU35" s="2" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="AV35" t="s">
         <v>33</v>
       </c>
       <c r="AY35" s="2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="AZ35" t="s">
         <v>33</v>
       </c>
       <c r="BC35" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="BD35" t="s">
         <v>33</v>
@@ -11519,7 +11528,7 @@
         <v>33</v>
       </c>
       <c r="BO35" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="BP35" t="s">
         <v>33</v>
@@ -11537,7 +11546,7 @@
         <v>33</v>
       </c>
       <c r="BW35" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="BX35" t="s">
         <v>33</v>
@@ -11563,25 +11572,25 @@
         <v>33</v>
       </c>
       <c r="AO36" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="AP36" t="s">
         <v>33</v>
       </c>
       <c r="AU36" s="2" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="AV36" t="s">
         <v>33</v>
       </c>
       <c r="AY36" s="2" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="AZ36" t="s">
         <v>33</v>
       </c>
       <c r="BC36" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="BD36" t="s">
         <v>33</v>
@@ -11611,7 +11620,7 @@
         <v>33</v>
       </c>
       <c r="BO36" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="BP36" t="s">
         <v>33</v>
@@ -11629,7 +11638,7 @@
         <v>33</v>
       </c>
       <c r="BW36" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="BX36" t="s">
         <v>33</v>
@@ -11655,25 +11664,25 @@
         <v>33</v>
       </c>
       <c r="AO37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="AP37" t="s">
         <v>33</v>
       </c>
       <c r="AU37" s="2" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="AV37" t="s">
         <v>33</v>
       </c>
       <c r="AY37" s="2" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="AZ37" t="s">
         <v>33</v>
       </c>
       <c r="BC37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="BD37" t="s">
         <v>33</v>
@@ -11703,7 +11712,7 @@
         <v>33</v>
       </c>
       <c r="BO37" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="BP37" t="s">
         <v>33</v>
@@ -11721,7 +11730,7 @@
         <v>33</v>
       </c>
       <c r="BW37" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="BX37" t="s">
         <v>33</v>
@@ -11747,25 +11756,25 @@
         <v>33</v>
       </c>
       <c r="AO38" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="AP38" t="s">
         <v>33</v>
       </c>
       <c r="AU38" s="2" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="AV38" t="s">
         <v>33</v>
       </c>
       <c r="AY38" s="2" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="AZ38" t="s">
         <v>33</v>
       </c>
       <c r="BC38" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="BD38" t="s">
         <v>33</v>
@@ -11795,7 +11804,7 @@
         <v>33</v>
       </c>
       <c r="BO38" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="BP38" t="s">
         <v>33</v>
@@ -11813,7 +11822,7 @@
         <v>33</v>
       </c>
       <c r="BW38" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="BX38" t="s">
         <v>33</v>
@@ -11839,25 +11848,25 @@
         <v>33</v>
       </c>
       <c r="AO39" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="AP39" t="s">
         <v>33</v>
       </c>
       <c r="AU39" s="2" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="AV39" t="s">
         <v>33</v>
       </c>
       <c r="AY39" s="2" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="AZ39" t="s">
         <v>33</v>
       </c>
       <c r="BC39" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="BD39" t="s">
         <v>33</v>
@@ -11887,7 +11896,7 @@
         <v>33</v>
       </c>
       <c r="BO39" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="BP39" t="s">
         <v>33</v>
@@ -11905,7 +11914,7 @@
         <v>33</v>
       </c>
       <c r="BW39" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="BX39" t="s">
         <v>33</v>
@@ -11931,25 +11940,25 @@
         <v>33</v>
       </c>
       <c r="AO40" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="AP40" t="s">
         <v>33</v>
       </c>
       <c r="AU40" s="2" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="AV40" t="s">
         <v>33</v>
       </c>
       <c r="AY40" s="2" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="AZ40" t="s">
         <v>33</v>
       </c>
       <c r="BC40" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="BD40" t="s">
         <v>33</v>
@@ -11979,7 +11988,7 @@
         <v>33</v>
       </c>
       <c r="BO40" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="BP40" t="s">
         <v>33</v>
@@ -11997,7 +12006,7 @@
         <v>33</v>
       </c>
       <c r="BW40" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="BX40" t="s">
         <v>33</v>
@@ -12023,19 +12032,19 @@
         <v>33</v>
       </c>
       <c r="AO41" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="AP41" t="s">
         <v>33</v>
       </c>
       <c r="AU41" s="2" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="AV41" t="s">
         <v>33</v>
       </c>
       <c r="BC41" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="BD41" t="s">
         <v>33</v>
@@ -12065,7 +12074,7 @@
         <v>33</v>
       </c>
       <c r="BO41" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="BP41" t="s">
         <v>33</v>
@@ -12083,7 +12092,7 @@
         <v>33</v>
       </c>
       <c r="BW41" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="BX41" t="s">
         <v>33</v>
@@ -12109,19 +12118,19 @@
         <v>33</v>
       </c>
       <c r="AO42" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="AP42" t="s">
         <v>33</v>
       </c>
       <c r="AU42" s="2" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="AV42" t="s">
         <v>33</v>
       </c>
       <c r="BC42" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="BD42" t="s">
         <v>33</v>
@@ -12151,7 +12160,7 @@
         <v>33</v>
       </c>
       <c r="BO42" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="BP42" t="s">
         <v>33</v>
@@ -12169,7 +12178,7 @@
         <v>33</v>
       </c>
       <c r="BW42" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="BX42" t="s">
         <v>33</v>
@@ -12195,19 +12204,19 @@
         <v>33</v>
       </c>
       <c r="AO43" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="AP43" t="s">
         <v>33</v>
       </c>
       <c r="AU43" s="2" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="AV43" t="s">
         <v>33</v>
       </c>
       <c r="BC43" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="BD43" t="s">
         <v>33</v>
@@ -12237,7 +12246,7 @@
         <v>33</v>
       </c>
       <c r="BO43" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="BP43" t="s">
         <v>33</v>
@@ -12255,7 +12264,7 @@
         <v>33</v>
       </c>
       <c r="BW43" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="BX43" t="s">
         <v>33</v>
@@ -12281,19 +12290,19 @@
         <v>33</v>
       </c>
       <c r="AO44" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="AP44" t="s">
         <v>33</v>
       </c>
       <c r="AU44" s="2" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="AV44" t="s">
         <v>33</v>
       </c>
       <c r="BC44" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="BD44" t="s">
         <v>33</v>
@@ -12323,7 +12332,7 @@
         <v>33</v>
       </c>
       <c r="BO44" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="BP44" t="s">
         <v>33</v>
@@ -12341,7 +12350,7 @@
         <v>33</v>
       </c>
       <c r="BW44" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="BX44" t="s">
         <v>33</v>
@@ -12367,19 +12376,19 @@
         <v>33</v>
       </c>
       <c r="AO45" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="AP45" t="s">
         <v>33</v>
       </c>
       <c r="AU45" s="2" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="AV45" t="s">
         <v>33</v>
       </c>
       <c r="BC45" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="BD45" t="s">
         <v>33</v>
@@ -12409,7 +12418,7 @@
         <v>33</v>
       </c>
       <c r="BO45" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="BP45" t="s">
         <v>33</v>
@@ -12427,7 +12436,7 @@
         <v>33</v>
       </c>
       <c r="BW45" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="BX45" t="s">
         <v>33</v>
@@ -12453,19 +12462,19 @@
         <v>33</v>
       </c>
       <c r="AO46" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="AP46" t="s">
         <v>33</v>
       </c>
       <c r="AU46" s="2" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="AV46" t="s">
         <v>33</v>
       </c>
       <c r="BC46" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="BD46" t="s">
         <v>33</v>
@@ -12495,7 +12504,7 @@
         <v>33</v>
       </c>
       <c r="BO46" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="BP46" t="s">
         <v>33</v>
@@ -12513,7 +12522,7 @@
         <v>33</v>
       </c>
       <c r="BW46" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="BX46" t="s">
         <v>33</v>
@@ -12539,19 +12548,19 @@
         <v>33</v>
       </c>
       <c r="AO47" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="AP47" t="s">
         <v>33</v>
       </c>
       <c r="AU47" s="2" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="AV47" t="s">
         <v>33</v>
       </c>
       <c r="BC47" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="BD47" t="s">
         <v>33</v>
@@ -12581,7 +12590,7 @@
         <v>33</v>
       </c>
       <c r="BO47" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="BP47" t="s">
         <v>33</v>
@@ -12599,7 +12608,7 @@
         <v>33</v>
       </c>
       <c r="BW47" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="BX47" t="s">
         <v>33</v>
@@ -12625,19 +12634,19 @@
         <v>33</v>
       </c>
       <c r="AO48" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="AP48" t="s">
         <v>33</v>
       </c>
       <c r="AU48" s="2" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="AV48" t="s">
         <v>33</v>
       </c>
       <c r="BC48" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="BD48" t="s">
         <v>33</v>
@@ -12667,7 +12676,7 @@
         <v>33</v>
       </c>
       <c r="BO48" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="BP48" t="s">
         <v>33</v>
@@ -12685,7 +12694,7 @@
         <v>33</v>
       </c>
       <c r="BW48" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="BX48" t="s">
         <v>33</v>
@@ -12711,19 +12720,19 @@
         <v>33</v>
       </c>
       <c r="AO49" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="AP49" t="s">
         <v>33</v>
       </c>
       <c r="AU49" s="2" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="AV49" t="s">
         <v>33</v>
       </c>
       <c r="BC49" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="BD49" t="s">
         <v>33</v>
@@ -12753,7 +12762,7 @@
         <v>33</v>
       </c>
       <c r="BO49" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="BP49" t="s">
         <v>33</v>
@@ -12771,7 +12780,7 @@
         <v>33</v>
       </c>
       <c r="BW49" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="BX49" t="s">
         <v>33</v>
@@ -12797,19 +12806,19 @@
         <v>33</v>
       </c>
       <c r="AO50" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="AP50" t="s">
         <v>33</v>
       </c>
       <c r="AU50" s="2" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="AV50" t="s">
         <v>33</v>
       </c>
       <c r="BC50" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="BD50" t="s">
         <v>33</v>
@@ -12839,7 +12848,7 @@
         <v>33</v>
       </c>
       <c r="BO50" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="BP50" t="s">
         <v>33</v>
@@ -12857,7 +12866,7 @@
         <v>33</v>
       </c>
       <c r="BW50" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="BX50" t="s">
         <v>33</v>
@@ -12883,19 +12892,19 @@
         <v>33</v>
       </c>
       <c r="AO51" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="AP51" t="s">
         <v>33</v>
       </c>
       <c r="AU51" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="AV51" t="s">
         <v>33</v>
       </c>
       <c r="BC51" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="BD51" t="s">
         <v>33</v>
@@ -12925,7 +12934,7 @@
         <v>33</v>
       </c>
       <c r="BO51" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="BP51" t="s">
         <v>33</v>
@@ -12943,7 +12952,7 @@
         <v>33</v>
       </c>
       <c r="BW51" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="BX51" t="s">
         <v>33</v>
@@ -12969,19 +12978,19 @@
         <v>33</v>
       </c>
       <c r="AO52" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="AP52" t="s">
         <v>33</v>
       </c>
       <c r="AU52" s="2" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="AV52" t="s">
         <v>33</v>
       </c>
       <c r="BC52" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="BD52" t="s">
         <v>33</v>
@@ -13011,7 +13020,7 @@
         <v>33</v>
       </c>
       <c r="BO52" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="BP52" t="s">
         <v>33</v>
@@ -13029,7 +13038,7 @@
         <v>33</v>
       </c>
       <c r="BW52" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="BX52" t="s">
         <v>33</v>
@@ -13055,19 +13064,19 @@
         <v>33</v>
       </c>
       <c r="AO53" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="AP53" t="s">
         <v>33</v>
       </c>
       <c r="AU53" s="2" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="AV53" t="s">
         <v>33</v>
       </c>
       <c r="BC53" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="BD53" t="s">
         <v>33</v>
@@ -13097,7 +13106,7 @@
         <v>33</v>
       </c>
       <c r="BO53" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="BP53" t="s">
         <v>33</v>
@@ -13115,7 +13124,7 @@
         <v>33</v>
       </c>
       <c r="BW53" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="BX53" t="s">
         <v>33</v>
@@ -13141,19 +13150,19 @@
         <v>33</v>
       </c>
       <c r="AO54" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="AP54" t="s">
         <v>33</v>
       </c>
       <c r="AU54" s="2" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="AV54" t="s">
         <v>33</v>
       </c>
       <c r="BC54" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="BD54" t="s">
         <v>33</v>
@@ -13183,7 +13192,7 @@
         <v>33</v>
       </c>
       <c r="BO54" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="BP54" t="s">
         <v>33</v>
@@ -13201,7 +13210,7 @@
         <v>33</v>
       </c>
       <c r="BW54" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="BX54" t="s">
         <v>33</v>
@@ -13227,19 +13236,19 @@
         <v>33</v>
       </c>
       <c r="AO55" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="AP55" t="s">
         <v>33</v>
       </c>
       <c r="AU55" s="2" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="AV55" t="s">
         <v>33</v>
       </c>
       <c r="BC55" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="BD55" t="s">
         <v>33</v>
@@ -13269,7 +13278,7 @@
         <v>33</v>
       </c>
       <c r="BO55" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="BP55" t="s">
         <v>33</v>
@@ -13287,7 +13296,7 @@
         <v>33</v>
       </c>
       <c r="BW55" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="BX55" t="s">
         <v>33</v>
@@ -13313,19 +13322,19 @@
         <v>33</v>
       </c>
       <c r="AO56" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="AP56" t="s">
         <v>33</v>
       </c>
       <c r="AU56" s="2" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="AV56" t="s">
         <v>33</v>
       </c>
       <c r="BC56" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="BD56" t="s">
         <v>33</v>
@@ -13355,7 +13364,7 @@
         <v>33</v>
       </c>
       <c r="BO56" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="BP56" t="s">
         <v>33</v>
@@ -13373,7 +13382,7 @@
         <v>33</v>
       </c>
       <c r="BW56" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="BX56" t="s">
         <v>33</v>
@@ -13399,19 +13408,19 @@
         <v>33</v>
       </c>
       <c r="AO57" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="AP57" t="s">
         <v>33</v>
       </c>
       <c r="AU57" s="2" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="AV57" t="s">
         <v>33</v>
       </c>
       <c r="BC57" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="BD57" t="s">
         <v>33</v>
@@ -13441,7 +13450,7 @@
         <v>33</v>
       </c>
       <c r="BO57" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="BP57" t="s">
         <v>33</v>
@@ -13459,7 +13468,7 @@
         <v>33</v>
       </c>
       <c r="BW57" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="BX57" t="s">
         <v>33</v>
@@ -13485,19 +13494,19 @@
         <v>33</v>
       </c>
       <c r="AO58" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="AP58" t="s">
         <v>33</v>
       </c>
       <c r="AU58" s="2" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="AV58" t="s">
         <v>33</v>
       </c>
       <c r="BC58" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="BD58" t="s">
         <v>33</v>
@@ -13527,7 +13536,7 @@
         <v>33</v>
       </c>
       <c r="BO58" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="BP58" t="s">
         <v>33</v>
@@ -13545,7 +13554,7 @@
         <v>33</v>
       </c>
       <c r="BW58" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="BX58" t="s">
         <v>33</v>
@@ -13571,19 +13580,19 @@
         <v>33</v>
       </c>
       <c r="AO59" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="AP59" t="s">
         <v>33</v>
       </c>
       <c r="AU59" s="2" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="AV59" t="s">
         <v>33</v>
       </c>
       <c r="BC59" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="BD59" t="s">
         <v>33</v>
@@ -13613,7 +13622,7 @@
         <v>33</v>
       </c>
       <c r="BO59" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="BP59" t="s">
         <v>33</v>
@@ -13631,7 +13640,7 @@
         <v>33</v>
       </c>
       <c r="BW59" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="BX59" t="s">
         <v>33</v>
@@ -13657,19 +13666,19 @@
         <v>33</v>
       </c>
       <c r="AO60" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="AP60" t="s">
         <v>33</v>
       </c>
       <c r="AU60" s="2" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="AV60" t="s">
         <v>33</v>
       </c>
       <c r="BC60" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="BD60" t="s">
         <v>33</v>
@@ -13717,7 +13726,7 @@
         <v>33</v>
       </c>
       <c r="BW60" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="BX60" t="s">
         <v>33</v>
@@ -13743,19 +13752,19 @@
         <v>33</v>
       </c>
       <c r="AO61" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="AP61" t="s">
         <v>33</v>
       </c>
       <c r="AU61" s="2" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="AV61" t="s">
         <v>33</v>
       </c>
       <c r="BC61" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="BD61" t="s">
         <v>33</v>
@@ -13785,7 +13794,7 @@
         <v>33</v>
       </c>
       <c r="BO61" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="BP61" t="s">
         <v>33</v>
@@ -13803,7 +13812,7 @@
         <v>33</v>
       </c>
       <c r="BW61" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="BX61" t="s">
         <v>33</v>
@@ -13829,19 +13838,19 @@
         <v>33</v>
       </c>
       <c r="AO62" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="AP62" t="s">
         <v>33</v>
       </c>
       <c r="AU62" s="2" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="AV62" t="s">
         <v>33</v>
       </c>
       <c r="BC62" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="BD62" t="s">
         <v>33</v>
@@ -13871,7 +13880,7 @@
         <v>33</v>
       </c>
       <c r="BO62" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="BP62" t="s">
         <v>33</v>
@@ -13889,7 +13898,7 @@
         <v>33</v>
       </c>
       <c r="BW62" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="BX62" t="s">
         <v>33</v>
@@ -13915,19 +13924,19 @@
         <v>33</v>
       </c>
       <c r="AO63" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="AP63" t="s">
         <v>33</v>
       </c>
       <c r="AU63" s="2" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="AV63" t="s">
         <v>33</v>
       </c>
       <c r="BC63" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="BD63" t="s">
         <v>33</v>
@@ -13957,7 +13966,7 @@
         <v>33</v>
       </c>
       <c r="BO63" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="BP63" t="s">
         <v>33</v>
@@ -13975,7 +13984,7 @@
         <v>33</v>
       </c>
       <c r="BW63" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="BX63" t="s">
         <v>33</v>
@@ -14001,19 +14010,19 @@
         <v>33</v>
       </c>
       <c r="AO64" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="AP64" t="s">
         <v>33</v>
       </c>
       <c r="AU64" s="2" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="AV64" t="s">
         <v>33</v>
       </c>
       <c r="BC64" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="BD64" t="s">
         <v>33</v>
@@ -14043,7 +14052,7 @@
         <v>33</v>
       </c>
       <c r="BO64" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="BP64" t="s">
         <v>33</v>
@@ -14061,7 +14070,7 @@
         <v>33</v>
       </c>
       <c r="BW64" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="BX64" t="s">
         <v>33</v>
@@ -14087,19 +14096,19 @@
         <v>33</v>
       </c>
       <c r="AO65" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="AP65" t="s">
         <v>33</v>
       </c>
       <c r="AU65" s="2" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="AV65" t="s">
         <v>33</v>
       </c>
       <c r="BC65" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="BD65" t="s">
         <v>33</v>
@@ -14129,7 +14138,7 @@
         <v>33</v>
       </c>
       <c r="BO65" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="BP65" t="s">
         <v>33</v>
@@ -14147,7 +14156,7 @@
         <v>33</v>
       </c>
       <c r="BW65" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="BX65" t="s">
         <v>33</v>
@@ -14173,19 +14182,19 @@
         <v>33</v>
       </c>
       <c r="AO66" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="AP66" t="s">
         <v>33</v>
       </c>
       <c r="AU66" s="2" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="AV66" t="s">
         <v>33</v>
       </c>
       <c r="BC66" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="BD66" t="s">
         <v>33</v>
@@ -14215,7 +14224,7 @@
         <v>33</v>
       </c>
       <c r="BO66" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="BP66" t="s">
         <v>33</v>
@@ -14233,7 +14242,7 @@
         <v>33</v>
       </c>
       <c r="BW66" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="BX66" t="s">
         <v>33</v>
@@ -14259,19 +14268,19 @@
         <v>33</v>
       </c>
       <c r="AO67" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="AP67" t="s">
         <v>33</v>
       </c>
       <c r="AU67" s="2" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="AV67" t="s">
         <v>33</v>
       </c>
       <c r="BC67" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="BD67" t="s">
         <v>33</v>
@@ -14301,7 +14310,7 @@
         <v>33</v>
       </c>
       <c r="BO67" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="BP67" t="s">
         <v>33</v>
@@ -14319,7 +14328,7 @@
         <v>33</v>
       </c>
       <c r="BW67" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="BX67" t="s">
         <v>33</v>
@@ -14345,19 +14354,19 @@
         <v>33</v>
       </c>
       <c r="AO68" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="AP68" t="s">
         <v>33</v>
       </c>
       <c r="AU68" s="2" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="AV68" t="s">
         <v>33</v>
       </c>
       <c r="BC68" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="BD68" t="s">
         <v>33</v>
@@ -14387,7 +14396,7 @@
         <v>33</v>
       </c>
       <c r="BO68" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="BP68" t="s">
         <v>33</v>
@@ -14405,7 +14414,7 @@
         <v>33</v>
       </c>
       <c r="BW68" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="BX68" t="s">
         <v>33</v>
@@ -14431,19 +14440,19 @@
         <v>33</v>
       </c>
       <c r="AO69" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="AP69" t="s">
         <v>33</v>
       </c>
       <c r="AU69" s="2" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="AV69" t="s">
         <v>33</v>
       </c>
       <c r="BC69" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="BD69" t="s">
         <v>33</v>
@@ -14473,7 +14482,7 @@
         <v>33</v>
       </c>
       <c r="BO69" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="BP69" t="s">
         <v>33</v>
@@ -14491,7 +14500,7 @@
         <v>33</v>
       </c>
       <c r="BW69" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="BX69" t="s">
         <v>33</v>
@@ -14511,19 +14520,19 @@
         <v>33</v>
       </c>
       <c r="AO70" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="AP70" t="s">
         <v>33</v>
       </c>
       <c r="AU70" s="2" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="AV70" t="s">
         <v>33</v>
       </c>
       <c r="BC70" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="BD70" t="s">
         <v>33</v>
@@ -14535,7 +14544,7 @@
         <v>33</v>
       </c>
       <c r="BO70" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="BP70" t="s">
         <v>33</v>
@@ -14547,7 +14556,7 @@
         <v>33</v>
       </c>
       <c r="BW70" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="BX70" t="s">
         <v>33</v>
@@ -14567,19 +14576,19 @@
         <v>33</v>
       </c>
       <c r="AO71" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="AP71" t="s">
         <v>33</v>
       </c>
       <c r="AU71" s="2" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="AV71" t="s">
         <v>33</v>
       </c>
       <c r="BC71" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="BD71" t="s">
         <v>33</v>
@@ -14591,7 +14600,7 @@
         <v>33</v>
       </c>
       <c r="BO71" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="BP71" t="s">
         <v>33</v>
@@ -14603,7 +14612,7 @@
         <v>33</v>
       </c>
       <c r="BW71" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="BX71" t="s">
         <v>33</v>
@@ -14623,19 +14632,19 @@
         <v>33</v>
       </c>
       <c r="AO72" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="AP72" t="s">
         <v>33</v>
       </c>
       <c r="AU72" s="2" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="AV72" t="s">
         <v>33</v>
       </c>
       <c r="BC72" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="BD72" t="s">
         <v>33</v>
@@ -14647,7 +14656,7 @@
         <v>33</v>
       </c>
       <c r="BO72" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="BP72" t="s">
         <v>33</v>
@@ -14659,7 +14668,7 @@
         <v>33</v>
       </c>
       <c r="BW72" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="BX72" t="s">
         <v>33</v>
@@ -14679,19 +14688,19 @@
         <v>33</v>
       </c>
       <c r="AO73" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="AP73" t="s">
         <v>33</v>
       </c>
       <c r="AU73" s="2" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="AV73" t="s">
         <v>33</v>
       </c>
       <c r="BC73" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="BD73" t="s">
         <v>33</v>
@@ -14703,7 +14712,7 @@
         <v>33</v>
       </c>
       <c r="BO73" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="BP73" t="s">
         <v>33</v>
@@ -14715,7 +14724,7 @@
         <v>33</v>
       </c>
       <c r="BW73" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="BX73" t="s">
         <v>33</v>
@@ -14735,19 +14744,19 @@
         <v>33</v>
       </c>
       <c r="AO74" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="AP74" t="s">
         <v>33</v>
       </c>
       <c r="AU74" s="2" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="AV74" t="s">
         <v>33</v>
       </c>
       <c r="BC74" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="BD74" t="s">
         <v>33</v>
@@ -14759,7 +14768,7 @@
         <v>33</v>
       </c>
       <c r="BO74" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="BP74" t="s">
         <v>33</v>
@@ -14771,7 +14780,7 @@
         <v>33</v>
       </c>
       <c r="BW74" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="BX74" t="s">
         <v>33</v>
@@ -14791,19 +14800,19 @@
         <v>33</v>
       </c>
       <c r="AO75" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="AP75" t="s">
         <v>33</v>
       </c>
       <c r="AU75" s="2" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="AV75" t="s">
         <v>33</v>
       </c>
       <c r="BC75" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="BD75" t="s">
         <v>33</v>
@@ -14815,7 +14824,7 @@
         <v>33</v>
       </c>
       <c r="BO75" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="BP75" t="s">
         <v>33</v>
@@ -14827,7 +14836,7 @@
         <v>33</v>
       </c>
       <c r="BW75" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="BX75" t="s">
         <v>33</v>
@@ -14847,19 +14856,19 @@
         <v>33</v>
       </c>
       <c r="AO76" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="AP76" t="s">
         <v>33</v>
       </c>
       <c r="AU76" s="2" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="AV76" t="s">
         <v>33</v>
       </c>
       <c r="BC76" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="BD76" t="s">
         <v>33</v>
@@ -14871,7 +14880,7 @@
         <v>33</v>
       </c>
       <c r="BO76" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="BP76" t="s">
         <v>33</v>
@@ -14883,7 +14892,7 @@
         <v>33</v>
       </c>
       <c r="BW76" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="BX76" t="s">
         <v>33</v>
@@ -14903,19 +14912,19 @@
         <v>33</v>
       </c>
       <c r="AO77" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="AP77" t="s">
         <v>33</v>
       </c>
       <c r="AU77" s="2" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="AV77" t="s">
         <v>33</v>
       </c>
       <c r="BC77" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="BD77" t="s">
         <v>33</v>
@@ -14927,7 +14936,7 @@
         <v>33</v>
       </c>
       <c r="BO77" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="BP77" t="s">
         <v>33</v>
@@ -14939,7 +14948,7 @@
         <v>33</v>
       </c>
       <c r="BW77" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="BX77" t="s">
         <v>33</v>
@@ -14959,19 +14968,19 @@
         <v>33</v>
       </c>
       <c r="AO78" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="AP78" t="s">
         <v>33</v>
       </c>
       <c r="AU78" s="2" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="AV78" t="s">
         <v>33</v>
       </c>
       <c r="BC78" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="BD78" t="s">
         <v>33</v>
@@ -14983,7 +14992,7 @@
         <v>33</v>
       </c>
       <c r="BO78" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="BP78" t="s">
         <v>33</v>
@@ -14995,7 +15004,7 @@
         <v>33</v>
       </c>
       <c r="BW78" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="BX78" t="s">
         <v>33</v>
@@ -15015,19 +15024,19 @@
         <v>33</v>
       </c>
       <c r="AO79" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="AP79" t="s">
         <v>33</v>
       </c>
       <c r="AU79" s="2" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="AV79" t="s">
         <v>33</v>
       </c>
       <c r="BC79" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="BD79" t="s">
         <v>33</v>
@@ -15039,7 +15048,7 @@
         <v>33</v>
       </c>
       <c r="BO79" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="BP79" t="s">
         <v>33</v>
@@ -15051,7 +15060,7 @@
         <v>33</v>
       </c>
       <c r="BW79" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="BX79" t="s">
         <v>33</v>
@@ -15071,19 +15080,19 @@
         <v>33</v>
       </c>
       <c r="AO80" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="AP80" t="s">
         <v>33</v>
       </c>
       <c r="AU80" s="2" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="AV80" t="s">
         <v>33</v>
       </c>
       <c r="BC80" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="BD80" t="s">
         <v>33</v>
@@ -15095,7 +15104,7 @@
         <v>33</v>
       </c>
       <c r="BO80" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="BP80" t="s">
         <v>33</v>
@@ -15107,7 +15116,7 @@
         <v>33</v>
       </c>
       <c r="BW80" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="BX80" t="s">
         <v>33</v>
@@ -15127,19 +15136,19 @@
         <v>33</v>
       </c>
       <c r="AO81" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="AP81" t="s">
         <v>33</v>
       </c>
       <c r="AU81" s="2" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="AV81" t="s">
         <v>33</v>
       </c>
       <c r="BC81" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="BD81" t="s">
         <v>33</v>
@@ -15151,7 +15160,7 @@
         <v>33</v>
       </c>
       <c r="BO81" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="BP81" t="s">
         <v>33</v>
@@ -15163,7 +15172,7 @@
         <v>33</v>
       </c>
       <c r="BW81" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="BX81" t="s">
         <v>33</v>
@@ -15183,19 +15192,19 @@
         <v>33</v>
       </c>
       <c r="AO82" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="AP82" t="s">
         <v>33</v>
       </c>
       <c r="AU82" s="2" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="AV82" t="s">
         <v>33</v>
       </c>
       <c r="BC82" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="BD82" t="s">
         <v>33</v>
@@ -15207,7 +15216,7 @@
         <v>33</v>
       </c>
       <c r="BO82" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="BP82" t="s">
         <v>33</v>
@@ -15219,7 +15228,7 @@
         <v>33</v>
       </c>
       <c r="BW82" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="BX82" t="s">
         <v>33</v>
@@ -15239,19 +15248,19 @@
         <v>33</v>
       </c>
       <c r="AO83" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="AP83" t="s">
         <v>33</v>
       </c>
       <c r="AU83" s="2" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="AV83" t="s">
         <v>33</v>
       </c>
       <c r="BC83" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="BD83" t="s">
         <v>33</v>
@@ -15263,7 +15272,7 @@
         <v>33</v>
       </c>
       <c r="BO83" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="BP83" t="s">
         <v>33</v>
@@ -15275,7 +15284,7 @@
         <v>33</v>
       </c>
       <c r="BW83" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="BX83" t="s">
         <v>33</v>
@@ -15295,19 +15304,19 @@
         <v>33</v>
       </c>
       <c r="AO84" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="AP84" t="s">
         <v>33</v>
       </c>
       <c r="AU84" s="2" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="AV84" t="s">
         <v>33</v>
       </c>
       <c r="BC84" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="BD84" t="s">
         <v>33</v>
@@ -15319,7 +15328,7 @@
         <v>33</v>
       </c>
       <c r="BO84" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="BP84" t="s">
         <v>33</v>
@@ -15331,7 +15340,7 @@
         <v>33</v>
       </c>
       <c r="BW84" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="BX84" t="s">
         <v>33</v>
@@ -15351,19 +15360,19 @@
         <v>33</v>
       </c>
       <c r="AO85" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="AP85" t="s">
         <v>33</v>
       </c>
       <c r="AU85" s="2" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="AV85" t="s">
         <v>33</v>
       </c>
       <c r="BC85" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="BD85" t="s">
         <v>33</v>
@@ -15375,7 +15384,7 @@
         <v>33</v>
       </c>
       <c r="BO85" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="BP85" t="s">
         <v>33</v>
@@ -15387,7 +15396,7 @@
         <v>33</v>
       </c>
       <c r="BW85" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="BX85" t="s">
         <v>33</v>
@@ -15407,19 +15416,19 @@
         <v>33</v>
       </c>
       <c r="AO86" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="AP86" t="s">
         <v>33</v>
       </c>
       <c r="AU86" s="2" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="AV86" t="s">
         <v>33</v>
       </c>
       <c r="BC86" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="BD86" t="s">
         <v>33</v>
@@ -15431,7 +15440,7 @@
         <v>33</v>
       </c>
       <c r="BO86" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="BP86" t="s">
         <v>33</v>
@@ -15443,7 +15452,7 @@
         <v>33</v>
       </c>
       <c r="BW86" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="BX86" t="s">
         <v>33</v>
@@ -15463,7 +15472,7 @@
         <v>33</v>
       </c>
       <c r="AU87" s="2" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="AV87" t="s">
         <v>33</v>
@@ -15475,7 +15484,7 @@
         <v>33</v>
       </c>
       <c r="BO87" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="BP87" t="s">
         <v>33</v>
@@ -15507,7 +15516,7 @@
         <v>33</v>
       </c>
       <c r="BO88" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="BP88" t="s">
         <v>33</v>
@@ -15539,7 +15548,7 @@
         <v>33</v>
       </c>
       <c r="BO89" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="BP89" t="s">
         <v>33</v>
@@ -15571,7 +15580,7 @@
         <v>33</v>
       </c>
       <c r="BO90" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="BP90" t="s">
         <v>33</v>
@@ -15603,7 +15612,7 @@
         <v>33</v>
       </c>
       <c r="BO91" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="BP91" t="s">
         <v>33</v>
@@ -15667,7 +15676,7 @@
         <v>33</v>
       </c>
       <c r="BO93" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="BP93" t="s">
         <v>33</v>
@@ -15699,7 +15708,7 @@
         <v>33</v>
       </c>
       <c r="BO94" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="BP94" t="s">
         <v>33</v>
@@ -15731,7 +15740,7 @@
         <v>33</v>
       </c>
       <c r="BO95" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="BP95" t="s">
         <v>33</v>
@@ -15763,7 +15772,7 @@
         <v>33</v>
       </c>
       <c r="BO96" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="BP96" t="s">
         <v>33</v>
@@ -15795,7 +15804,7 @@
         <v>33</v>
       </c>
       <c r="BO97" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="BP97" t="s">
         <v>33</v>
@@ -15827,7 +15836,7 @@
         <v>33</v>
       </c>
       <c r="BO98" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="BP98" t="s">
         <v>33</v>
@@ -15859,7 +15868,7 @@
         <v>33</v>
       </c>
       <c r="BO99" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="BP99" t="s">
         <v>33</v>
@@ -15891,7 +15900,7 @@
         <v>33</v>
       </c>
       <c r="BO100" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="BP100" t="s">
         <v>33</v>
@@ -15923,7 +15932,7 @@
         <v>33</v>
       </c>
       <c r="BO101" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="BP101" t="s">
         <v>33</v>
@@ -15955,7 +15964,7 @@
         <v>33</v>
       </c>
       <c r="BO102" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="BP102" t="s">
         <v>33</v>
@@ -15987,7 +15996,7 @@
         <v>33</v>
       </c>
       <c r="BO103" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="BP103" t="s">
         <v>33</v>
@@ -16019,7 +16028,7 @@
         <v>33</v>
       </c>
       <c r="BO104" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="BP104" t="s">
         <v>33</v>
@@ -16051,7 +16060,7 @@
         <v>33</v>
       </c>
       <c r="BO105" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="BP105" t="s">
         <v>33</v>
@@ -16083,7 +16092,7 @@
         <v>33</v>
       </c>
       <c r="BO106" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="BP106" t="s">
         <v>33</v>
@@ -16115,7 +16124,7 @@
         <v>33</v>
       </c>
       <c r="BO107" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="BP107" t="s">
         <v>33</v>
@@ -16147,7 +16156,7 @@
         <v>33</v>
       </c>
       <c r="BO108" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="BP108" t="s">
         <v>33</v>
@@ -16179,7 +16188,7 @@
         <v>33</v>
       </c>
       <c r="BO109" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="BP109" t="s">
         <v>33</v>
@@ -16211,7 +16220,7 @@
         <v>33</v>
       </c>
       <c r="BO110" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="BP110" t="s">
         <v>33</v>
@@ -16243,7 +16252,7 @@
         <v>33</v>
       </c>
       <c r="BO111" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="BP111" t="s">
         <v>33</v>
@@ -16275,7 +16284,7 @@
         <v>33</v>
       </c>
       <c r="BO112" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="BP112" t="s">
         <v>33</v>
@@ -16307,7 +16316,7 @@
         <v>33</v>
       </c>
       <c r="BO113" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="BP113" t="s">
         <v>33</v>
@@ -16339,7 +16348,7 @@
         <v>33</v>
       </c>
       <c r="BO114" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="BP114" t="s">
         <v>33</v>
@@ -16371,7 +16380,7 @@
         <v>33</v>
       </c>
       <c r="BO115" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="BP115" t="s">
         <v>33</v>
@@ -16403,7 +16412,7 @@
         <v>33</v>
       </c>
       <c r="BO116" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="BP116" t="s">
         <v>33</v>
@@ -16435,7 +16444,7 @@
         <v>33</v>
       </c>
       <c r="BO117" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="BP117" t="s">
         <v>33</v>
@@ -16467,7 +16476,7 @@
         <v>33</v>
       </c>
       <c r="BO118" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="BP118" t="s">
         <v>33</v>
@@ -16499,7 +16508,7 @@
         <v>33</v>
       </c>
       <c r="BO119" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="BP119" t="s">
         <v>33</v>
@@ -16531,7 +16540,7 @@
         <v>33</v>
       </c>
       <c r="BO120" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="BP120" t="s">
         <v>33</v>
@@ -16563,7 +16572,7 @@
         <v>33</v>
       </c>
       <c r="BO121" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="BP121" t="s">
         <v>33</v>
@@ -16595,7 +16604,7 @@
         <v>33</v>
       </c>
       <c r="BO122" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="BP122" t="s">
         <v>33</v>
@@ -16627,7 +16636,7 @@
         <v>33</v>
       </c>
       <c r="BO123" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="BP123" t="s">
         <v>33</v>
@@ -16659,7 +16668,7 @@
         <v>33</v>
       </c>
       <c r="BO124" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="BP124" t="s">
         <v>33</v>
@@ -16691,7 +16700,7 @@
         <v>33</v>
       </c>
       <c r="BO125" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="BP125" t="s">
         <v>33</v>
@@ -16723,7 +16732,7 @@
         <v>33</v>
       </c>
       <c r="BO126" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="BP126" t="s">
         <v>33</v>
@@ -16755,7 +16764,7 @@
         <v>33</v>
       </c>
       <c r="BO127" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="BP127" t="s">
         <v>33</v>
@@ -16787,7 +16796,7 @@
         <v>33</v>
       </c>
       <c r="BO128" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="BP128" t="s">
         <v>33</v>
@@ -16819,7 +16828,7 @@
         <v>33</v>
       </c>
       <c r="BO129" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="BP129" t="s">
         <v>33</v>
@@ -16851,7 +16860,7 @@
         <v>33</v>
       </c>
       <c r="BO130" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="BP130" t="s">
         <v>33</v>
@@ -16883,7 +16892,7 @@
         <v>33</v>
       </c>
       <c r="BO131" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="BP131" t="s">
         <v>33</v>
@@ -16915,7 +16924,7 @@
         <v>33</v>
       </c>
       <c r="BO132" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="BP132" t="s">
         <v>33</v>
@@ -16947,7 +16956,7 @@
         <v>33</v>
       </c>
       <c r="BO133" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="BP133" t="s">
         <v>33</v>
@@ -16979,7 +16988,7 @@
         <v>33</v>
       </c>
       <c r="BO134" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="BP134" t="s">
         <v>33</v>
@@ -17011,7 +17020,7 @@
         <v>33</v>
       </c>
       <c r="BO135" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="BP135" t="s">
         <v>33</v>
@@ -17043,7 +17052,7 @@
         <v>33</v>
       </c>
       <c r="BO136" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="BP136" t="s">
         <v>33</v>
@@ -17075,7 +17084,7 @@
         <v>33</v>
       </c>
       <c r="BO137" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="BP137" t="s">
         <v>33</v>
@@ -17101,7 +17110,7 @@
         <v>33</v>
       </c>
       <c r="BO138" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="BP138" t="s">
         <v>33</v>
@@ -17127,7 +17136,7 @@
         <v>33</v>
       </c>
       <c r="BO139" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="BP139" t="s">
         <v>33</v>
@@ -17153,7 +17162,7 @@
         <v>33</v>
       </c>
       <c r="BO140" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="BP140" t="s">
         <v>33</v>
@@ -17179,7 +17188,7 @@
         <v>33</v>
       </c>
       <c r="BO141" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="BP141" t="s">
         <v>33</v>
@@ -17231,7 +17240,7 @@
         <v>33</v>
       </c>
       <c r="BO143" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="BP143" t="s">
         <v>33</v>
@@ -17257,7 +17266,7 @@
         <v>33</v>
       </c>
       <c r="BO144" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="BP144" t="s">
         <v>33</v>
@@ -17283,7 +17292,7 @@
         <v>33</v>
       </c>
       <c r="BO145" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="BP145" t="s">
         <v>33</v>
@@ -17309,7 +17318,7 @@
         <v>33</v>
       </c>
       <c r="BO146" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="BP146" t="s">
         <v>33</v>
@@ -17335,7 +17344,7 @@
         <v>33</v>
       </c>
       <c r="BO147" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="BP147" t="s">
         <v>33</v>
@@ -17361,7 +17370,7 @@
         <v>33</v>
       </c>
       <c r="BO148" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="BP148" t="s">
         <v>33</v>
@@ -17387,7 +17396,7 @@
         <v>33</v>
       </c>
       <c r="BO149" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="BP149" t="s">
         <v>33</v>
@@ -17413,7 +17422,7 @@
         <v>33</v>
       </c>
       <c r="BO150" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="BP150" t="s">
         <v>33</v>
@@ -17439,7 +17448,7 @@
         <v>33</v>
       </c>
       <c r="BO151" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="BP151" t="s">
         <v>33</v>
@@ -17465,7 +17474,7 @@
         <v>33</v>
       </c>
       <c r="BO152" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="BP152" t="s">
         <v>33</v>
@@ -17491,7 +17500,7 @@
         <v>33</v>
       </c>
       <c r="BO153" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="BP153" t="s">
         <v>33</v>
@@ -17517,7 +17526,7 @@
         <v>33</v>
       </c>
       <c r="BO154" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="BP154" t="s">
         <v>33</v>
@@ -17543,7 +17552,7 @@
         <v>33</v>
       </c>
       <c r="BO155" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="BP155" t="s">
         <v>33</v>
@@ -17569,7 +17578,7 @@
         <v>33</v>
       </c>
       <c r="BO156" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="BP156" t="s">
         <v>33</v>
@@ -17595,7 +17604,7 @@
         <v>33</v>
       </c>
       <c r="BO157" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="BP157" t="s">
         <v>33</v>
@@ -17621,7 +17630,7 @@
         <v>33</v>
       </c>
       <c r="BO158" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="BP158" t="s">
         <v>33</v>
@@ -17647,7 +17656,7 @@
         <v>33</v>
       </c>
       <c r="BO159" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="BP159" t="s">
         <v>33</v>
@@ -17673,7 +17682,7 @@
         <v>33</v>
       </c>
       <c r="BO160" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="BP160" t="s">
         <v>33</v>
@@ -17699,7 +17708,7 @@
         <v>33</v>
       </c>
       <c r="BO161" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="BP161" t="s">
         <v>33</v>
@@ -17725,7 +17734,7 @@
         <v>33</v>
       </c>
       <c r="BO162" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="BP162" t="s">
         <v>33</v>
@@ -17751,7 +17760,7 @@
         <v>33</v>
       </c>
       <c r="BO163" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="BP163" t="s">
         <v>33</v>
@@ -17777,7 +17786,7 @@
         <v>33</v>
       </c>
       <c r="BO164" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="BP164" t="s">
         <v>33</v>
@@ -17803,7 +17812,7 @@
         <v>33</v>
       </c>
       <c r="BO165" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="BP165" t="s">
         <v>33</v>
@@ -17829,7 +17838,7 @@
         <v>33</v>
       </c>
       <c r="BO166" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="BP166" t="s">
         <v>33</v>
@@ -17855,7 +17864,7 @@
         <v>33</v>
       </c>
       <c r="BO167" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="BP167" t="s">
         <v>33</v>
@@ -17881,7 +17890,7 @@
         <v>33</v>
       </c>
       <c r="BO168" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="BP168" t="s">
         <v>33</v>
@@ -17907,7 +17916,7 @@
         <v>33</v>
       </c>
       <c r="BO169" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="BP169" t="s">
         <v>33</v>
@@ -17933,7 +17942,7 @@
         <v>33</v>
       </c>
       <c r="BO170" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="BP170" t="s">
         <v>33</v>
@@ -17959,7 +17968,7 @@
         <v>33</v>
       </c>
       <c r="BO171" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="BP171" t="s">
         <v>33</v>
@@ -17985,7 +17994,7 @@
         <v>33</v>
       </c>
       <c r="BO172" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="BP172" t="s">
         <v>33</v>
@@ -18011,7 +18020,7 @@
         <v>33</v>
       </c>
       <c r="BO173" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="BP173" t="s">
         <v>33</v>
@@ -18037,7 +18046,7 @@
         <v>33</v>
       </c>
       <c r="BO174" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="BP174" t="s">
         <v>33</v>
@@ -18063,7 +18072,7 @@
         <v>33</v>
       </c>
       <c r="BO175" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="BP175" t="s">
         <v>33</v>
@@ -18089,7 +18098,7 @@
         <v>33</v>
       </c>
       <c r="BO176" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="BP176" t="s">
         <v>33</v>
@@ -18115,7 +18124,7 @@
         <v>33</v>
       </c>
       <c r="BO177" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="BP177" t="s">
         <v>33</v>
@@ -18141,7 +18150,7 @@
         <v>33</v>
       </c>
       <c r="BO178" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="BP178" t="s">
         <v>33</v>
@@ -18167,7 +18176,7 @@
         <v>33</v>
       </c>
       <c r="BO179" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="BP179" t="s">
         <v>33</v>
@@ -18193,7 +18202,7 @@
         <v>33</v>
       </c>
       <c r="BO180" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="BP180" t="s">
         <v>33</v>
@@ -18219,7 +18228,7 @@
         <v>33</v>
       </c>
       <c r="BO181" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="BP181" t="s">
         <v>33</v>
@@ -18245,7 +18254,7 @@
         <v>33</v>
       </c>
       <c r="BO182" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="BP182" t="s">
         <v>33</v>
@@ -18271,7 +18280,7 @@
         <v>33</v>
       </c>
       <c r="BO183" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="BP183" t="s">
         <v>33</v>
@@ -35665,7 +35674,7 @@
       <formula1>-146096</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T9:T1000001">
-      <formula1>'Codelijsten'!$AG$4:$AG$8</formula1>
+      <formula1>'Codelijsten'!$AG$4:$AG$9</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -35709,55 +35718,55 @@
         <v>11</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="2" spans="1:18" hidden="1">
@@ -35765,32 +35774,32 @@
         <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -35798,7 +35807,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="R2" s="1"/>
     </row>
@@ -35813,30 +35822,30 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M3" s="7"/>
       <c r="N3" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>292</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="7" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="4" spans="1:18" hidden="1">
@@ -35844,13 +35853,13 @@
         <v>282</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="5" spans="1:18" hidden="1"/>
@@ -35868,55 +35877,55 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
   </sheetData>
@@ -35962,7 +35971,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BG6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54.7109375" style="3" customWidth="1"/>
@@ -36022,207 +36031,203 @@
     <col min="57" max="57" width="34.7109375" style="3" customWidth="1"/>
     <col min="58" max="58" width="48.7109375" style="3" customWidth="1"/>
     <col min="59" max="59" width="40.7109375" customWidth="1"/>
-    <col min="60" max="60" width="10.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" hidden="1">
+    <row r="1" spans="1:59" hidden="1">
       <c r="A1" s="6" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>1416</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="2" spans="1:60" hidden="1">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="2" spans="1:59" hidden="1">
       <c r="A2" s="7" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
@@ -36234,22 +36239,22 @@
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
       <c r="R2" s="7" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="S2" s="7"/>
       <c r="T2" s="7" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="U2" s="7"/>
       <c r="V2" s="7"/>
       <c r="W2" s="7" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
@@ -36262,13 +36267,13 @@
       <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
       <c r="AN2" s="1" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1"/>
@@ -36276,7 +36281,7 @@
         <v>30</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
@@ -36285,7 +36290,7 @@
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
@@ -36295,19 +36300,16 @@
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
-      <c r="BH2" s="1" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="3" spans="1:60" hidden="1">
+    </row>
+    <row r="3" spans="1:59" hidden="1">
       <c r="A3" s="7" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>23</v>
@@ -36317,13 +36319,13 @@
         <v>11</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -36344,7 +36346,7 @@
       <c r="U3" s="7"/>
       <c r="V3" s="7"/>
       <c r="Y3" s="1" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1"/>
@@ -36354,12 +36356,12 @@
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="AH3" s="1"/>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="7" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="AK3" s="7" t="s">
         <v>23</v>
@@ -36369,19 +36371,19 @@
         <v>11</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="AR3" s="7" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
@@ -36391,35 +36393,35 @@
         <v>282</v>
       </c>
       <c r="AY3" s="7" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="AZ3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="BA3" s="7"/>
       <c r="BB3" s="1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="BF3" s="1" t="s">
         <v>292</v>
       </c>
       <c r="BG3" s="1"/>
     </row>
-    <row r="4" spans="1:60" hidden="1">
+    <row r="4" spans="1:59" hidden="1">
       <c r="E4" s="7" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>11</v>
@@ -36429,7 +36431,7 @@
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -36439,10 +36441,10 @@
         <v>282</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="Y4" s="7" t="s">
         <v>11</v>
@@ -36452,7 +36454,7 @@
       </c>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -36464,272 +36466,269 @@
       <c r="AH4" s="7"/>
       <c r="AI4" s="7"/>
       <c r="AK4" s="7" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="AL4" s="7" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="AS4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="AT4" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="AU4" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AV4" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="AW4" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="AZ4" s="1" t="s">
         <v>282</v>
       </c>
       <c r="BA4" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="BF4" s="7" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="BG4" s="7" t="s">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="5" spans="1:60" hidden="1">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="5" spans="1:59" hidden="1">
       <c r="K5" s="7" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="AB5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="AG5" s="7" t="s">
         <v>282</v>
       </c>
       <c r="AH5" s="7" t="s">
+        <v>1596</v>
+      </c>
+      <c r="AI5" s="7" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:59">
+      <c r="A6" s="6" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>1566</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>1594</v>
+      </c>
+      <c r="U6" s="6" t="s">
         <v>1595</v>
       </c>
-      <c r="AI5" s="7" t="s">
+      <c r="V6" s="6" t="s">
         <v>1597</v>
       </c>
-    </row>
-    <row r="6" spans="1:60">
-      <c r="A6" s="6" t="s">
-        <v>1557</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>1559</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>1561</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>1562</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>1565</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>1567</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>1569</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>1571</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>1573</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>1574</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>1578</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>1579</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>1583</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>1585</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>1590</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>1591</v>
-      </c>
-      <c r="T6" s="6" t="s">
-        <v>1593</v>
-      </c>
-      <c r="U6" s="6" t="s">
-        <v>1594</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>1596</v>
-      </c>
       <c r="W6" s="6" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="AG6" s="1" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="AH6" s="1" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="AL6" s="1" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="AM6" s="1" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="AN6" s="1" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="AO6" s="1" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="AP6" s="1" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="AQ6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="AR6" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="AS6" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="AT6" s="1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="AU6" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="AV6" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="AW6" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="AX6" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="AY6" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="AZ6" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="BA6" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="BB6" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="BC6" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="BD6" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BE6" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="BF6" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="BG6" s="1" t="s">
-        <v>1416</v>
-      </c>
-      <c r="BH6" s="1" t="s">
-        <v>1566</v>
+        <v>1417</v>
       </c>
     </row>
   </sheetData>
@@ -36892,82 +36891,82 @@
   <sheetData>
     <row r="1" spans="1:74" hidden="1">
       <c r="A1" s="6" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>294</v>
@@ -36979,136 +36978,136 @@
         <v>296</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>1308</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="BV1" s="1" t="s">
         <v>30</v>
@@ -37138,20 +37137,20 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>294</v>
@@ -37163,19 +37162,19 @@
         <v>296</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>1308</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -37190,24 +37189,24 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
       <c r="AU2" s="1" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="BG2" s="1"/>
       <c r="BH2" s="1"/>
@@ -37216,7 +37215,7 @@
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
       <c r="BM2" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1"/>
@@ -37238,10 +37237,10 @@
         <v>289</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -37255,18 +37254,18 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="V3" s="7" t="s">
         <v>23</v>
@@ -37276,14 +37275,14 @@
         <v>11</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -37293,16 +37292,16 @@
       <c r="AS3" s="1"/>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="AY3" s="7" t="s">
         <v>287</v>
@@ -37315,19 +37314,19 @@
         <v>298</v>
       </c>
       <c r="BC3" s="7" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="BD3" s="7" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="BE3" s="1" t="s">
         <v>282</v>
       </c>
       <c r="BF3" s="7" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="BG3" s="1" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="BH3" s="1"/>
       <c r="BI3" s="1"/>
@@ -37337,23 +37336,23 @@
         <v>282</v>
       </c>
       <c r="BM3" s="7" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="BN3" s="7" t="s">
         <v>23</v>
       </c>
       <c r="BO3" s="7"/>
       <c r="BP3" s="1" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="BQ3" s="1" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="BS3" s="1" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="BT3" s="1" t="s">
         <v>292</v>
@@ -37362,13 +37361,13 @@
     </row>
     <row r="4" spans="1:74" hidden="1">
       <c r="D4" s="7" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -37378,36 +37377,36 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="1" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="V4" s="7" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="AH4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="AL4" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="AM4" s="7" t="s">
         <v>11</v>
@@ -37417,7 +37416,7 @@
       </c>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
@@ -37427,34 +37426,34 @@
         <v>289</v>
       </c>
       <c r="BA4" s="7" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="BG4" s="7" t="s">
         <v>11</v>
       </c>
       <c r="BH4" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="BI4" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="BJ4" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="BK4" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="BN4" s="1" t="s">
         <v>282</v>
       </c>
       <c r="BO4" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="BT4" s="7" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="BU4" s="7" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="5" spans="1:74" hidden="1">
@@ -37467,146 +37466,146 @@
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="1" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="P5" s="7" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="AN5" s="7" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="AO5" s="7" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="AP5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="AQ5" s="1" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="AT5" s="1" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="6" spans="1:74" hidden="1">
       <c r="F6" s="7" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="7" spans="1:74">
       <c r="A7" s="6" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>294</v>
@@ -37618,136 +37617,136 @@
         <v>296</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>1308</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="AG7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="BA7" s="1" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="BE7" s="1" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="BF7" s="1" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="BG7" s="1" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="BH7" s="1" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="BI7" s="1" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="BJ7" s="1" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="BK7" s="1" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="BL7" s="1" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="BM7" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="BN7" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="BO7" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="BP7" s="1" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="BQ7" s="1" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="BR7" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="BS7" s="1" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="BT7" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="BU7" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="BV7" s="1" t="s">
         <v>30</v>
@@ -37851,50 +37850,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B2" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B3" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="B4" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B5" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="B6" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
     </row>
   </sheetData>

--- a/templates/productie/productie_grondwater_template.xlsx
+++ b/templates/productie/productie_grondwater_template.xlsx
@@ -6185,13 +6185,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:50:29.723209</t>
+    <t>2026-05-06 16:21:08.764246</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>

--- a/templates/productie/productie_grondwater_template.xlsx
+++ b/templates/productie/productie_grondwater_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9245" uniqueCount="2065">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9249" uniqueCount="2067">
   <si>
     <t>identificatie</t>
   </si>
@@ -5276,6 +5276,12 @@
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bam</t>
   </si>
   <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbb</t>
+  </si>
+  <si>
+    <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/bbo</t>
+  </si>
+  <si>
     <t>https://data.bodemenondergrond.vlaanderen.be/id/concept/bemonsteringsprocedure/boc</t>
   </si>
   <si>
@@ -6185,19 +6191,19 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-06 16:21:08.764246</t>
+    <t>2026-05-19 11:28:40.395214</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.1</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>xdov-version</t>
   </si>
   <si>
-    <t>10.1.0</t>
+    <t>10.2.0</t>
   </si>
   <si>
     <t>schema-version</t>
@@ -6500,7 +6506,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table25" displayName="Table25" ref="AW3:AX12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="Table25" displayName="Table25" ref="AW3:AX14" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Code"/>
     <tableColumn id="2" name="Beschrijving"/>
@@ -7052,7 +7058,7 @@
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
@@ -7204,15 +7210,15 @@
       </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1" t="s">
@@ -7224,7 +7230,7 @@
       </c>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1" t="s">
@@ -7232,11 +7238,11 @@
       </c>
       <c r="BR2" s="1"/>
       <c r="BS2" s="1" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="BT2" s="1"/>
       <c r="BU2" s="1" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="BV2" s="1"/>
       <c r="BW2" s="1" t="s">
@@ -7626,13 +7632,13 @@
         <v>33</v>
       </c>
       <c r="AY4" s="2" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="AZ4" t="s">
         <v>33</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="BB4" t="s">
         <v>33</v>
@@ -7674,13 +7680,13 @@
         <v>33</v>
       </c>
       <c r="BO4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="BP4" t="s">
         <v>33</v>
       </c>
       <c r="BQ4" s="2" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="BR4" t="s">
         <v>33</v>
@@ -7856,13 +7862,13 @@
         <v>33</v>
       </c>
       <c r="AY5" s="2" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="AZ5" t="s">
         <v>33</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="BB5" t="s">
         <v>33</v>
@@ -7904,13 +7910,13 @@
         <v>33</v>
       </c>
       <c r="BO5" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="BP5" t="s">
         <v>33</v>
       </c>
       <c r="BQ5" s="2" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="BR5" t="s">
         <v>33</v>
@@ -8068,13 +8074,13 @@
         <v>33</v>
       </c>
       <c r="AY6" s="2" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="AZ6" t="s">
         <v>33</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="BB6" t="s">
         <v>33</v>
@@ -8116,13 +8122,13 @@
         <v>33</v>
       </c>
       <c r="BO6" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="BP6" t="s">
         <v>33</v>
       </c>
       <c r="BQ6" s="2" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="BR6" t="s">
         <v>33</v>
@@ -8262,7 +8268,7 @@
         <v>33</v>
       </c>
       <c r="AY7" s="2" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="AZ7" t="s">
         <v>33</v>
@@ -8298,7 +8304,7 @@
         <v>33</v>
       </c>
       <c r="BO7" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="BP7" t="s">
         <v>33</v>
@@ -8432,7 +8438,7 @@
         <v>33</v>
       </c>
       <c r="AY8" s="2" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="AZ8" t="s">
         <v>33</v>
@@ -8468,7 +8474,7 @@
         <v>33</v>
       </c>
       <c r="BO8" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="BP8" t="s">
         <v>33</v>
@@ -8596,7 +8602,7 @@
         <v>33</v>
       </c>
       <c r="AY9" s="2" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="AZ9" t="s">
         <v>33</v>
@@ -8632,7 +8638,7 @@
         <v>33</v>
       </c>
       <c r="BO9" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="BP9" t="s">
         <v>33</v>
@@ -8754,7 +8760,7 @@
         <v>33</v>
       </c>
       <c r="AY10" s="2" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="AZ10" t="s">
         <v>33</v>
@@ -8790,7 +8796,7 @@
         <v>33</v>
       </c>
       <c r="BO10" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="BP10" t="s">
         <v>33</v>
@@ -8894,7 +8900,7 @@
         <v>33</v>
       </c>
       <c r="AY11" s="2" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="AZ11" t="s">
         <v>33</v>
@@ -8930,7 +8936,7 @@
         <v>33</v>
       </c>
       <c r="BO11" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="BP11" t="s">
         <v>33</v>
@@ -9034,7 +9040,7 @@
         <v>33</v>
       </c>
       <c r="AY12" s="2" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="AZ12" t="s">
         <v>33</v>
@@ -9070,7 +9076,7 @@
         <v>33</v>
       </c>
       <c r="BO12" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="BP12" t="s">
         <v>33</v>
@@ -9167,8 +9173,14 @@
       <c r="AV13" t="s">
         <v>33</v>
       </c>
+      <c r="AW13" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>33</v>
+      </c>
       <c r="AY13" s="2" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="AZ13" t="s">
         <v>33</v>
@@ -9204,7 +9216,7 @@
         <v>33</v>
       </c>
       <c r="BO13" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="BP13" t="s">
         <v>33</v>
@@ -9301,8 +9313,14 @@
       <c r="AV14" t="s">
         <v>33</v>
       </c>
+      <c r="AW14" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>33</v>
+      </c>
       <c r="AY14" s="2" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="AZ14" t="s">
         <v>33</v>
@@ -9338,7 +9356,7 @@
         <v>33</v>
       </c>
       <c r="BO14" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="BP14" t="s">
         <v>33</v>
@@ -9436,7 +9454,7 @@
         <v>33</v>
       </c>
       <c r="AY15" s="2" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="AZ15" t="s">
         <v>33</v>
@@ -9472,7 +9490,7 @@
         <v>33</v>
       </c>
       <c r="BO15" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="BP15" t="s">
         <v>33</v>
@@ -9570,7 +9588,7 @@
         <v>33</v>
       </c>
       <c r="AY16" s="2" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="AZ16" t="s">
         <v>33</v>
@@ -9606,7 +9624,7 @@
         <v>33</v>
       </c>
       <c r="BO16" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="BP16" t="s">
         <v>33</v>
@@ -9698,7 +9716,7 @@
         <v>33</v>
       </c>
       <c r="AY17" s="2" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="AZ17" t="s">
         <v>33</v>
@@ -9734,7 +9752,7 @@
         <v>33</v>
       </c>
       <c r="BO17" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="BP17" t="s">
         <v>33</v>
@@ -9820,7 +9838,7 @@
         <v>33</v>
       </c>
       <c r="AY18" s="2" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="AZ18" t="s">
         <v>33</v>
@@ -9856,7 +9874,7 @@
         <v>33</v>
       </c>
       <c r="BO18" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="BP18" t="s">
         <v>33</v>
@@ -9930,7 +9948,7 @@
         <v>33</v>
       </c>
       <c r="AY19" s="2" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="AZ19" t="s">
         <v>33</v>
@@ -10040,7 +10058,7 @@
         <v>33</v>
       </c>
       <c r="AY20" s="2" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="AZ20" t="s">
         <v>33</v>
@@ -10076,7 +10094,7 @@
         <v>33</v>
       </c>
       <c r="BO20" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="BP20" t="s">
         <v>33</v>
@@ -10144,7 +10162,7 @@
         <v>33</v>
       </c>
       <c r="AY21" s="2" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="AZ21" t="s">
         <v>33</v>
@@ -10180,7 +10198,7 @@
         <v>33</v>
       </c>
       <c r="BO21" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="BP21" t="s">
         <v>33</v>
@@ -10248,7 +10266,7 @@
         <v>33</v>
       </c>
       <c r="AY22" s="2" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="AZ22" t="s">
         <v>33</v>
@@ -10284,7 +10302,7 @@
         <v>33</v>
       </c>
       <c r="BO22" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="BP22" t="s">
         <v>33</v>
@@ -10352,7 +10370,7 @@
         <v>33</v>
       </c>
       <c r="AY23" s="2" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="AZ23" t="s">
         <v>33</v>
@@ -10388,7 +10406,7 @@
         <v>33</v>
       </c>
       <c r="BO23" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="BP23" t="s">
         <v>33</v>
@@ -10450,7 +10468,7 @@
         <v>33</v>
       </c>
       <c r="AY24" s="2" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="AZ24" t="s">
         <v>33</v>
@@ -10486,7 +10504,7 @@
         <v>33</v>
       </c>
       <c r="BO24" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="BP24" t="s">
         <v>33</v>
@@ -10548,7 +10566,7 @@
         <v>33</v>
       </c>
       <c r="AY25" s="2" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="AZ25" t="s">
         <v>33</v>
@@ -10584,7 +10602,7 @@
         <v>33</v>
       </c>
       <c r="BO25" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="BP25" t="s">
         <v>33</v>
@@ -10646,7 +10664,7 @@
         <v>33</v>
       </c>
       <c r="AY26" s="2" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="AZ26" t="s">
         <v>33</v>
@@ -10682,7 +10700,7 @@
         <v>33</v>
       </c>
       <c r="BO26" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="BP26" t="s">
         <v>33</v>
@@ -10744,7 +10762,7 @@
         <v>33</v>
       </c>
       <c r="AY27" s="2" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="AZ27" t="s">
         <v>33</v>
@@ -10780,7 +10798,7 @@
         <v>33</v>
       </c>
       <c r="BO27" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="BP27" t="s">
         <v>33</v>
@@ -10842,7 +10860,7 @@
         <v>33</v>
       </c>
       <c r="AY28" s="2" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="AZ28" t="s">
         <v>33</v>
@@ -10878,7 +10896,7 @@
         <v>33</v>
       </c>
       <c r="BO28" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="BP28" t="s">
         <v>33</v>
@@ -10940,7 +10958,7 @@
         <v>33</v>
       </c>
       <c r="AY29" s="2" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="AZ29" t="s">
         <v>33</v>
@@ -10976,7 +10994,7 @@
         <v>33</v>
       </c>
       <c r="BO29" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="BP29" t="s">
         <v>33</v>
@@ -11032,7 +11050,7 @@
         <v>33</v>
       </c>
       <c r="AY30" s="2" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="AZ30" t="s">
         <v>33</v>
@@ -11068,7 +11086,7 @@
         <v>33</v>
       </c>
       <c r="BO30" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="BP30" t="s">
         <v>33</v>
@@ -11124,7 +11142,7 @@
         <v>33</v>
       </c>
       <c r="AY31" s="2" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="AZ31" t="s">
         <v>33</v>
@@ -11160,7 +11178,7 @@
         <v>33</v>
       </c>
       <c r="BO31" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="BP31" t="s">
         <v>33</v>
@@ -11216,7 +11234,7 @@
         <v>33</v>
       </c>
       <c r="AY32" s="2" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="AZ32" t="s">
         <v>33</v>
@@ -11252,7 +11270,7 @@
         <v>33</v>
       </c>
       <c r="BO32" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="BP32" t="s">
         <v>33</v>
@@ -11308,7 +11326,7 @@
         <v>33</v>
       </c>
       <c r="AY33" s="2" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="AZ33" t="s">
         <v>33</v>
@@ -11344,7 +11362,7 @@
         <v>33</v>
       </c>
       <c r="BO33" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="BP33" t="s">
         <v>33</v>
@@ -11400,7 +11418,7 @@
         <v>33</v>
       </c>
       <c r="AY34" s="2" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="AZ34" t="s">
         <v>33</v>
@@ -11436,7 +11454,7 @@
         <v>33</v>
       </c>
       <c r="BO34" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="BP34" t="s">
         <v>33</v>
@@ -11492,7 +11510,7 @@
         <v>33</v>
       </c>
       <c r="AY35" s="2" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="AZ35" t="s">
         <v>33</v>
@@ -11528,7 +11546,7 @@
         <v>33</v>
       </c>
       <c r="BO35" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="BP35" t="s">
         <v>33</v>
@@ -11584,7 +11602,7 @@
         <v>33</v>
       </c>
       <c r="AY36" s="2" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="AZ36" t="s">
         <v>33</v>
@@ -11620,7 +11638,7 @@
         <v>33</v>
       </c>
       <c r="BO36" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="BP36" t="s">
         <v>33</v>
@@ -11676,7 +11694,7 @@
         <v>33</v>
       </c>
       <c r="AY37" s="2" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="AZ37" t="s">
         <v>33</v>
@@ -11712,7 +11730,7 @@
         <v>33</v>
       </c>
       <c r="BO37" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="BP37" t="s">
         <v>33</v>
@@ -11768,7 +11786,7 @@
         <v>33</v>
       </c>
       <c r="AY38" s="2" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="AZ38" t="s">
         <v>33</v>
@@ -11804,7 +11822,7 @@
         <v>33</v>
       </c>
       <c r="BO38" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="BP38" t="s">
         <v>33</v>
@@ -11860,7 +11878,7 @@
         <v>33</v>
       </c>
       <c r="AY39" s="2" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="AZ39" t="s">
         <v>33</v>
@@ -11896,7 +11914,7 @@
         <v>33</v>
       </c>
       <c r="BO39" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="BP39" t="s">
         <v>33</v>
@@ -11952,7 +11970,7 @@
         <v>33</v>
       </c>
       <c r="AY40" s="2" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="AZ40" t="s">
         <v>33</v>
@@ -11988,7 +12006,7 @@
         <v>33</v>
       </c>
       <c r="BO40" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="BP40" t="s">
         <v>33</v>
@@ -12074,7 +12092,7 @@
         <v>33</v>
       </c>
       <c r="BO41" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="BP41" t="s">
         <v>33</v>
@@ -12160,7 +12178,7 @@
         <v>33</v>
       </c>
       <c r="BO42" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="BP42" t="s">
         <v>33</v>
@@ -12246,7 +12264,7 @@
         <v>33</v>
       </c>
       <c r="BO43" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="BP43" t="s">
         <v>33</v>
@@ -12332,7 +12350,7 @@
         <v>33</v>
       </c>
       <c r="BO44" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="BP44" t="s">
         <v>33</v>
@@ -12418,7 +12436,7 @@
         <v>33</v>
       </c>
       <c r="BO45" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="BP45" t="s">
         <v>33</v>
@@ -12504,7 +12522,7 @@
         <v>33</v>
       </c>
       <c r="BO46" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="BP46" t="s">
         <v>33</v>
@@ -12590,7 +12608,7 @@
         <v>33</v>
       </c>
       <c r="BO47" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="BP47" t="s">
         <v>33</v>
@@ -12676,7 +12694,7 @@
         <v>33</v>
       </c>
       <c r="BO48" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="BP48" t="s">
         <v>33</v>
@@ -12762,7 +12780,7 @@
         <v>33</v>
       </c>
       <c r="BO49" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="BP49" t="s">
         <v>33</v>
@@ -12848,7 +12866,7 @@
         <v>33</v>
       </c>
       <c r="BO50" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="BP50" t="s">
         <v>33</v>
@@ -12934,7 +12952,7 @@
         <v>33</v>
       </c>
       <c r="BO51" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="BP51" t="s">
         <v>33</v>
@@ -13020,7 +13038,7 @@
         <v>33</v>
       </c>
       <c r="BO52" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="BP52" t="s">
         <v>33</v>
@@ -13106,7 +13124,7 @@
         <v>33</v>
       </c>
       <c r="BO53" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="BP53" t="s">
         <v>33</v>
@@ -13192,7 +13210,7 @@
         <v>33</v>
       </c>
       <c r="BO54" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="BP54" t="s">
         <v>33</v>
@@ -13278,7 +13296,7 @@
         <v>33</v>
       </c>
       <c r="BO55" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="BP55" t="s">
         <v>33</v>
@@ -13364,7 +13382,7 @@
         <v>33</v>
       </c>
       <c r="BO56" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="BP56" t="s">
         <v>33</v>
@@ -13450,7 +13468,7 @@
         <v>33</v>
       </c>
       <c r="BO57" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="BP57" t="s">
         <v>33</v>
@@ -13536,7 +13554,7 @@
         <v>33</v>
       </c>
       <c r="BO58" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="BP58" t="s">
         <v>33</v>
@@ -13622,7 +13640,7 @@
         <v>33</v>
       </c>
       <c r="BO59" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="BP59" t="s">
         <v>33</v>
@@ -13794,7 +13812,7 @@
         <v>33</v>
       </c>
       <c r="BO61" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="BP61" t="s">
         <v>33</v>
@@ -13880,7 +13898,7 @@
         <v>33</v>
       </c>
       <c r="BO62" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="BP62" t="s">
         <v>33</v>
@@ -13966,7 +13984,7 @@
         <v>33</v>
       </c>
       <c r="BO63" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="BP63" t="s">
         <v>33</v>
@@ -14052,7 +14070,7 @@
         <v>33</v>
       </c>
       <c r="BO64" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="BP64" t="s">
         <v>33</v>
@@ -14138,7 +14156,7 @@
         <v>33</v>
       </c>
       <c r="BO65" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="BP65" t="s">
         <v>33</v>
@@ -14224,7 +14242,7 @@
         <v>33</v>
       </c>
       <c r="BO66" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="BP66" t="s">
         <v>33</v>
@@ -14310,7 +14328,7 @@
         <v>33</v>
       </c>
       <c r="BO67" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="BP67" t="s">
         <v>33</v>
@@ -14396,7 +14414,7 @@
         <v>33</v>
       </c>
       <c r="BO68" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="BP68" t="s">
         <v>33</v>
@@ -14482,7 +14500,7 @@
         <v>33</v>
       </c>
       <c r="BO69" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="BP69" t="s">
         <v>33</v>
@@ -14544,7 +14562,7 @@
         <v>33</v>
       </c>
       <c r="BO70" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="BP70" t="s">
         <v>33</v>
@@ -14600,7 +14618,7 @@
         <v>33</v>
       </c>
       <c r="BO71" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="BP71" t="s">
         <v>33</v>
@@ -14656,7 +14674,7 @@
         <v>33</v>
       </c>
       <c r="BO72" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="BP72" t="s">
         <v>33</v>
@@ -14712,7 +14730,7 @@
         <v>33</v>
       </c>
       <c r="BO73" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="BP73" t="s">
         <v>33</v>
@@ -14768,7 +14786,7 @@
         <v>33</v>
       </c>
       <c r="BO74" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="BP74" t="s">
         <v>33</v>
@@ -14824,7 +14842,7 @@
         <v>33</v>
       </c>
       <c r="BO75" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="BP75" t="s">
         <v>33</v>
@@ -14880,7 +14898,7 @@
         <v>33</v>
       </c>
       <c r="BO76" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="BP76" t="s">
         <v>33</v>
@@ -14936,7 +14954,7 @@
         <v>33</v>
       </c>
       <c r="BO77" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="BP77" t="s">
         <v>33</v>
@@ -14992,7 +15010,7 @@
         <v>33</v>
       </c>
       <c r="BO78" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="BP78" t="s">
         <v>33</v>
@@ -15048,7 +15066,7 @@
         <v>33</v>
       </c>
       <c r="BO79" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="BP79" t="s">
         <v>33</v>
@@ -15104,7 +15122,7 @@
         <v>33</v>
       </c>
       <c r="BO80" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="BP80" t="s">
         <v>33</v>
@@ -15160,7 +15178,7 @@
         <v>33</v>
       </c>
       <c r="BO81" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="BP81" t="s">
         <v>33</v>
@@ -15216,7 +15234,7 @@
         <v>33</v>
       </c>
       <c r="BO82" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="BP82" t="s">
         <v>33</v>
@@ -15272,7 +15290,7 @@
         <v>33</v>
       </c>
       <c r="BO83" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="BP83" t="s">
         <v>33</v>
@@ -15328,7 +15346,7 @@
         <v>33</v>
       </c>
       <c r="BO84" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="BP84" t="s">
         <v>33</v>
@@ -15384,7 +15402,7 @@
         <v>33</v>
       </c>
       <c r="BO85" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="BP85" t="s">
         <v>33</v>
@@ -15440,7 +15458,7 @@
         <v>33</v>
       </c>
       <c r="BO86" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="BP86" t="s">
         <v>33</v>
@@ -15484,7 +15502,7 @@
         <v>33</v>
       </c>
       <c r="BO87" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="BP87" t="s">
         <v>33</v>
@@ -15516,7 +15534,7 @@
         <v>33</v>
       </c>
       <c r="BO88" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="BP88" t="s">
         <v>33</v>
@@ -15548,7 +15566,7 @@
         <v>33</v>
       </c>
       <c r="BO89" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="BP89" t="s">
         <v>33</v>
@@ -15580,7 +15598,7 @@
         <v>33</v>
       </c>
       <c r="BO90" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="BP90" t="s">
         <v>33</v>
@@ -15612,7 +15630,7 @@
         <v>33</v>
       </c>
       <c r="BO91" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="BP91" t="s">
         <v>33</v>
@@ -15676,7 +15694,7 @@
         <v>33</v>
       </c>
       <c r="BO93" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="BP93" t="s">
         <v>33</v>
@@ -15708,7 +15726,7 @@
         <v>33</v>
       </c>
       <c r="BO94" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="BP94" t="s">
         <v>33</v>
@@ -15740,7 +15758,7 @@
         <v>33</v>
       </c>
       <c r="BO95" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="BP95" t="s">
         <v>33</v>
@@ -15772,7 +15790,7 @@
         <v>33</v>
       </c>
       <c r="BO96" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="BP96" t="s">
         <v>33</v>
@@ -15804,7 +15822,7 @@
         <v>33</v>
       </c>
       <c r="BO97" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="BP97" t="s">
         <v>33</v>
@@ -15836,7 +15854,7 @@
         <v>33</v>
       </c>
       <c r="BO98" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="BP98" t="s">
         <v>33</v>
@@ -15868,7 +15886,7 @@
         <v>33</v>
       </c>
       <c r="BO99" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="BP99" t="s">
         <v>33</v>
@@ -15900,7 +15918,7 @@
         <v>33</v>
       </c>
       <c r="BO100" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="BP100" t="s">
         <v>33</v>
@@ -15932,7 +15950,7 @@
         <v>33</v>
       </c>
       <c r="BO101" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="BP101" t="s">
         <v>33</v>
@@ -15964,7 +15982,7 @@
         <v>33</v>
       </c>
       <c r="BO102" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="BP102" t="s">
         <v>33</v>
@@ -15996,7 +16014,7 @@
         <v>33</v>
       </c>
       <c r="BO103" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="BP103" t="s">
         <v>33</v>
@@ -16028,7 +16046,7 @@
         <v>33</v>
       </c>
       <c r="BO104" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="BP104" t="s">
         <v>33</v>
@@ -16060,7 +16078,7 @@
         <v>33</v>
       </c>
       <c r="BO105" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="BP105" t="s">
         <v>33</v>
@@ -16092,7 +16110,7 @@
         <v>33</v>
       </c>
       <c r="BO106" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="BP106" t="s">
         <v>33</v>
@@ -16124,7 +16142,7 @@
         <v>33</v>
       </c>
       <c r="BO107" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="BP107" t="s">
         <v>33</v>
@@ -16156,7 +16174,7 @@
         <v>33</v>
       </c>
       <c r="BO108" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="BP108" t="s">
         <v>33</v>
@@ -16188,7 +16206,7 @@
         <v>33</v>
       </c>
       <c r="BO109" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="BP109" t="s">
         <v>33</v>
@@ -16220,7 +16238,7 @@
         <v>33</v>
       </c>
       <c r="BO110" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="BP110" t="s">
         <v>33</v>
@@ -16252,7 +16270,7 @@
         <v>33</v>
       </c>
       <c r="BO111" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="BP111" t="s">
         <v>33</v>
@@ -16284,7 +16302,7 @@
         <v>33</v>
       </c>
       <c r="BO112" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="BP112" t="s">
         <v>33</v>
@@ -16316,7 +16334,7 @@
         <v>33</v>
       </c>
       <c r="BO113" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="BP113" t="s">
         <v>33</v>
@@ -16348,7 +16366,7 @@
         <v>33</v>
       </c>
       <c r="BO114" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="BP114" t="s">
         <v>33</v>
@@ -16380,7 +16398,7 @@
         <v>33</v>
       </c>
       <c r="BO115" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="BP115" t="s">
         <v>33</v>
@@ -16412,7 +16430,7 @@
         <v>33</v>
       </c>
       <c r="BO116" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="BP116" t="s">
         <v>33</v>
@@ -16444,7 +16462,7 @@
         <v>33</v>
       </c>
       <c r="BO117" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="BP117" t="s">
         <v>33</v>
@@ -16476,7 +16494,7 @@
         <v>33</v>
       </c>
       <c r="BO118" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="BP118" t="s">
         <v>33</v>
@@ -16508,7 +16526,7 @@
         <v>33</v>
       </c>
       <c r="BO119" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="BP119" t="s">
         <v>33</v>
@@ -16540,7 +16558,7 @@
         <v>33</v>
       </c>
       <c r="BO120" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="BP120" t="s">
         <v>33</v>
@@ -16572,7 +16590,7 @@
         <v>33</v>
       </c>
       <c r="BO121" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="BP121" t="s">
         <v>33</v>
@@ -16604,7 +16622,7 @@
         <v>33</v>
       </c>
       <c r="BO122" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="BP122" t="s">
         <v>33</v>
@@ -16636,7 +16654,7 @@
         <v>33</v>
       </c>
       <c r="BO123" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="BP123" t="s">
         <v>33</v>
@@ -16668,7 +16686,7 @@
         <v>33</v>
       </c>
       <c r="BO124" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="BP124" t="s">
         <v>33</v>
@@ -16700,7 +16718,7 @@
         <v>33</v>
       </c>
       <c r="BO125" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="BP125" t="s">
         <v>33</v>
@@ -16732,7 +16750,7 @@
         <v>33</v>
       </c>
       <c r="BO126" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="BP126" t="s">
         <v>33</v>
@@ -16764,7 +16782,7 @@
         <v>33</v>
       </c>
       <c r="BO127" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="BP127" t="s">
         <v>33</v>
@@ -16796,7 +16814,7 @@
         <v>33</v>
       </c>
       <c r="BO128" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="BP128" t="s">
         <v>33</v>
@@ -16828,7 +16846,7 @@
         <v>33</v>
       </c>
       <c r="BO129" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="BP129" t="s">
         <v>33</v>
@@ -16860,7 +16878,7 @@
         <v>33</v>
       </c>
       <c r="BO130" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="BP130" t="s">
         <v>33</v>
@@ -16892,7 +16910,7 @@
         <v>33</v>
       </c>
       <c r="BO131" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="BP131" t="s">
         <v>33</v>
@@ -16924,7 +16942,7 @@
         <v>33</v>
       </c>
       <c r="BO132" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="BP132" t="s">
         <v>33</v>
@@ -16956,7 +16974,7 @@
         <v>33</v>
       </c>
       <c r="BO133" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="BP133" t="s">
         <v>33</v>
@@ -16988,7 +17006,7 @@
         <v>33</v>
       </c>
       <c r="BO134" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="BP134" t="s">
         <v>33</v>
@@ -17020,7 +17038,7 @@
         <v>33</v>
       </c>
       <c r="BO135" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="BP135" t="s">
         <v>33</v>
@@ -17052,7 +17070,7 @@
         <v>33</v>
       </c>
       <c r="BO136" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="BP136" t="s">
         <v>33</v>
@@ -17084,7 +17102,7 @@
         <v>33</v>
       </c>
       <c r="BO137" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="BP137" t="s">
         <v>33</v>
@@ -17110,7 +17128,7 @@
         <v>33</v>
       </c>
       <c r="BO138" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="BP138" t="s">
         <v>33</v>
@@ -17136,7 +17154,7 @@
         <v>33</v>
       </c>
       <c r="BO139" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="BP139" t="s">
         <v>33</v>
@@ -17162,7 +17180,7 @@
         <v>33</v>
       </c>
       <c r="BO140" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="BP140" t="s">
         <v>33</v>
@@ -17188,7 +17206,7 @@
         <v>33</v>
       </c>
       <c r="BO141" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="BP141" t="s">
         <v>33</v>
@@ -17240,7 +17258,7 @@
         <v>33</v>
       </c>
       <c r="BO143" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="BP143" t="s">
         <v>33</v>
@@ -17266,7 +17284,7 @@
         <v>33</v>
       </c>
       <c r="BO144" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="BP144" t="s">
         <v>33</v>
@@ -17292,7 +17310,7 @@
         <v>33</v>
       </c>
       <c r="BO145" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="BP145" t="s">
         <v>33</v>
@@ -17318,7 +17336,7 @@
         <v>33</v>
       </c>
       <c r="BO146" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="BP146" t="s">
         <v>33</v>
@@ -17344,7 +17362,7 @@
         <v>33</v>
       </c>
       <c r="BO147" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="BP147" t="s">
         <v>33</v>
@@ -17370,7 +17388,7 @@
         <v>33</v>
       </c>
       <c r="BO148" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="BP148" t="s">
         <v>33</v>
@@ -17396,7 +17414,7 @@
         <v>33</v>
       </c>
       <c r="BO149" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="BP149" t="s">
         <v>33</v>
@@ -17422,7 +17440,7 @@
         <v>33</v>
       </c>
       <c r="BO150" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="BP150" t="s">
         <v>33</v>
@@ -17448,7 +17466,7 @@
         <v>33</v>
       </c>
       <c r="BO151" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="BP151" t="s">
         <v>33</v>
@@ -17474,7 +17492,7 @@
         <v>33</v>
       </c>
       <c r="BO152" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="BP152" t="s">
         <v>33</v>
@@ -17500,7 +17518,7 @@
         <v>33</v>
       </c>
       <c r="BO153" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="BP153" t="s">
         <v>33</v>
@@ -17526,7 +17544,7 @@
         <v>33</v>
       </c>
       <c r="BO154" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="BP154" t="s">
         <v>33</v>
@@ -17552,7 +17570,7 @@
         <v>33</v>
       </c>
       <c r="BO155" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="BP155" t="s">
         <v>33</v>
@@ -17578,7 +17596,7 @@
         <v>33</v>
       </c>
       <c r="BO156" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="BP156" t="s">
         <v>33</v>
@@ -17604,7 +17622,7 @@
         <v>33</v>
       </c>
       <c r="BO157" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="BP157" t="s">
         <v>33</v>
@@ -17630,7 +17648,7 @@
         <v>33</v>
       </c>
       <c r="BO158" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="BP158" t="s">
         <v>33</v>
@@ -17656,7 +17674,7 @@
         <v>33</v>
       </c>
       <c r="BO159" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="BP159" t="s">
         <v>33</v>
@@ -17682,7 +17700,7 @@
         <v>33</v>
       </c>
       <c r="BO160" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="BP160" t="s">
         <v>33</v>
@@ -17708,7 +17726,7 @@
         <v>33</v>
       </c>
       <c r="BO161" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="BP161" t="s">
         <v>33</v>
@@ -17734,7 +17752,7 @@
         <v>33</v>
       </c>
       <c r="BO162" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="BP162" t="s">
         <v>33</v>
@@ -17760,7 +17778,7 @@
         <v>33</v>
       </c>
       <c r="BO163" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="BP163" t="s">
         <v>33</v>
@@ -17786,7 +17804,7 @@
         <v>33</v>
       </c>
       <c r="BO164" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="BP164" t="s">
         <v>33</v>
@@ -17812,7 +17830,7 @@
         <v>33</v>
       </c>
       <c r="BO165" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="BP165" t="s">
         <v>33</v>
@@ -17838,7 +17856,7 @@
         <v>33</v>
       </c>
       <c r="BO166" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="BP166" t="s">
         <v>33</v>
@@ -17864,7 +17882,7 @@
         <v>33</v>
       </c>
       <c r="BO167" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="BP167" t="s">
         <v>33</v>
@@ -17890,7 +17908,7 @@
         <v>33</v>
       </c>
       <c r="BO168" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="BP168" t="s">
         <v>33</v>
@@ -17916,7 +17934,7 @@
         <v>33</v>
       </c>
       <c r="BO169" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="BP169" t="s">
         <v>33</v>
@@ -17942,7 +17960,7 @@
         <v>33</v>
       </c>
       <c r="BO170" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="BP170" t="s">
         <v>33</v>
@@ -17968,7 +17986,7 @@
         <v>33</v>
       </c>
       <c r="BO171" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="BP171" t="s">
         <v>33</v>
@@ -17994,7 +18012,7 @@
         <v>33</v>
       </c>
       <c r="BO172" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="BP172" t="s">
         <v>33</v>
@@ -18020,7 +18038,7 @@
         <v>33</v>
       </c>
       <c r="BO173" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="BP173" t="s">
         <v>33</v>
@@ -18046,7 +18064,7 @@
         <v>33</v>
       </c>
       <c r="BO174" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="BP174" t="s">
         <v>33</v>
@@ -18072,7 +18090,7 @@
         <v>33</v>
       </c>
       <c r="BO175" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="BP175" t="s">
         <v>33</v>
@@ -18098,7 +18116,7 @@
         <v>33</v>
       </c>
       <c r="BO176" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="BP176" t="s">
         <v>33</v>
@@ -18124,7 +18142,7 @@
         <v>33</v>
       </c>
       <c r="BO177" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="BP177" t="s">
         <v>33</v>
@@ -18150,7 +18168,7 @@
         <v>33</v>
       </c>
       <c r="BO178" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="BP178" t="s">
         <v>33</v>
@@ -18176,7 +18194,7 @@
         <v>33</v>
       </c>
       <c r="BO179" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="BP179" t="s">
         <v>33</v>
@@ -18202,7 +18220,7 @@
         <v>33</v>
       </c>
       <c r="BO180" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="BP180" t="s">
         <v>33</v>
@@ -18228,7 +18246,7 @@
         <v>33</v>
       </c>
       <c r="BO181" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="BP181" t="s">
         <v>33</v>
@@ -18254,7 +18272,7 @@
         <v>33</v>
       </c>
       <c r="BO182" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="BP182" t="s">
         <v>33</v>
@@ -18280,7 +18298,7 @@
         <v>33</v>
       </c>
       <c r="BO183" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="BP183" t="s">
         <v>33</v>
@@ -34734,113 +34752,113 @@
     <hyperlink ref="AW12" r:id="rId32"/>
     <hyperlink ref="AY12" r:id="rId33"/>
     <hyperlink ref="AU13" r:id="rId34"/>
-    <hyperlink ref="AY13" r:id="rId35"/>
-    <hyperlink ref="AU14" r:id="rId36"/>
-    <hyperlink ref="AY14" r:id="rId37"/>
-    <hyperlink ref="AU15" r:id="rId38"/>
-    <hyperlink ref="AY15" r:id="rId39"/>
-    <hyperlink ref="AU16" r:id="rId40"/>
-    <hyperlink ref="AY16" r:id="rId41"/>
-    <hyperlink ref="AU17" r:id="rId42"/>
-    <hyperlink ref="AY17" r:id="rId43"/>
-    <hyperlink ref="AU18" r:id="rId44"/>
-    <hyperlink ref="AY18" r:id="rId45"/>
-    <hyperlink ref="AU19" r:id="rId46"/>
-    <hyperlink ref="AY19" r:id="rId47"/>
-    <hyperlink ref="AU20" r:id="rId48"/>
-    <hyperlink ref="AY20" r:id="rId49"/>
-    <hyperlink ref="AU21" r:id="rId50"/>
-    <hyperlink ref="AY21" r:id="rId51"/>
-    <hyperlink ref="AU22" r:id="rId52"/>
-    <hyperlink ref="AY22" r:id="rId53"/>
-    <hyperlink ref="AU23" r:id="rId54"/>
-    <hyperlink ref="AY23" r:id="rId55"/>
-    <hyperlink ref="AU24" r:id="rId56"/>
-    <hyperlink ref="AY24" r:id="rId57"/>
-    <hyperlink ref="AU25" r:id="rId58"/>
-    <hyperlink ref="AY25" r:id="rId59"/>
-    <hyperlink ref="AU26" r:id="rId60"/>
-    <hyperlink ref="AY26" r:id="rId61"/>
-    <hyperlink ref="AU27" r:id="rId62"/>
-    <hyperlink ref="AY27" r:id="rId63"/>
-    <hyperlink ref="AU28" r:id="rId64"/>
-    <hyperlink ref="AY28" r:id="rId65"/>
-    <hyperlink ref="AU29" r:id="rId66"/>
-    <hyperlink ref="AY29" r:id="rId67"/>
-    <hyperlink ref="AU30" r:id="rId68"/>
-    <hyperlink ref="AY30" r:id="rId69"/>
-    <hyperlink ref="AU31" r:id="rId70"/>
-    <hyperlink ref="AY31" r:id="rId71"/>
-    <hyperlink ref="AU32" r:id="rId72"/>
-    <hyperlink ref="AY32" r:id="rId73"/>
-    <hyperlink ref="AU33" r:id="rId74"/>
-    <hyperlink ref="AY33" r:id="rId75"/>
-    <hyperlink ref="AU34" r:id="rId76"/>
-    <hyperlink ref="AY34" r:id="rId77"/>
-    <hyperlink ref="AU35" r:id="rId78"/>
-    <hyperlink ref="AY35" r:id="rId79"/>
-    <hyperlink ref="AU36" r:id="rId80"/>
-    <hyperlink ref="AY36" r:id="rId81"/>
-    <hyperlink ref="AU37" r:id="rId82"/>
-    <hyperlink ref="AY37" r:id="rId83"/>
-    <hyperlink ref="AU38" r:id="rId84"/>
-    <hyperlink ref="AY38" r:id="rId85"/>
-    <hyperlink ref="AU39" r:id="rId86"/>
-    <hyperlink ref="AY39" r:id="rId87"/>
-    <hyperlink ref="AU40" r:id="rId88"/>
-    <hyperlink ref="AY40" r:id="rId89"/>
-    <hyperlink ref="AU41" r:id="rId90"/>
-    <hyperlink ref="AU42" r:id="rId91"/>
-    <hyperlink ref="AU43" r:id="rId92"/>
-    <hyperlink ref="AU44" r:id="rId93"/>
-    <hyperlink ref="AU45" r:id="rId94"/>
-    <hyperlink ref="AU46" r:id="rId95"/>
-    <hyperlink ref="AU47" r:id="rId96"/>
-    <hyperlink ref="AU48" r:id="rId97"/>
-    <hyperlink ref="AU49" r:id="rId98"/>
-    <hyperlink ref="AU50" r:id="rId99"/>
-    <hyperlink ref="AU51" r:id="rId100"/>
-    <hyperlink ref="AU52" r:id="rId101"/>
-    <hyperlink ref="AU53" r:id="rId102"/>
-    <hyperlink ref="AU54" r:id="rId103"/>
-    <hyperlink ref="AU55" r:id="rId104"/>
-    <hyperlink ref="AU56" r:id="rId105"/>
-    <hyperlink ref="AU57" r:id="rId106"/>
-    <hyperlink ref="AU58" r:id="rId107"/>
-    <hyperlink ref="AU59" r:id="rId108"/>
-    <hyperlink ref="AU60" r:id="rId109"/>
-    <hyperlink ref="AU61" r:id="rId110"/>
-    <hyperlink ref="AU62" r:id="rId111"/>
-    <hyperlink ref="AU63" r:id="rId112"/>
-    <hyperlink ref="AU64" r:id="rId113"/>
-    <hyperlink ref="AU65" r:id="rId114"/>
-    <hyperlink ref="AU66" r:id="rId115"/>
-    <hyperlink ref="AU67" r:id="rId116"/>
-    <hyperlink ref="AU68" r:id="rId117"/>
-    <hyperlink ref="AU69" r:id="rId118"/>
-    <hyperlink ref="AU70" r:id="rId119"/>
-    <hyperlink ref="AU71" r:id="rId120"/>
-    <hyperlink ref="AU72" r:id="rId121"/>
-    <hyperlink ref="AU73" r:id="rId122"/>
-    <hyperlink ref="AU74" r:id="rId123"/>
-    <hyperlink ref="AU75" r:id="rId124"/>
-    <hyperlink ref="AU76" r:id="rId125"/>
-    <hyperlink ref="AU77" r:id="rId126"/>
-    <hyperlink ref="AU78" r:id="rId127"/>
-    <hyperlink ref="AU79" r:id="rId128"/>
-    <hyperlink ref="AU80" r:id="rId129"/>
-    <hyperlink ref="AU81" r:id="rId130"/>
-    <hyperlink ref="AU82" r:id="rId131"/>
-    <hyperlink ref="AU83" r:id="rId132"/>
-    <hyperlink ref="AU84" r:id="rId133"/>
-    <hyperlink ref="AU85" r:id="rId134"/>
-    <hyperlink ref="AU86" r:id="rId135"/>
-    <hyperlink ref="AU87" r:id="rId136"/>
+    <hyperlink ref="AW13" r:id="rId35"/>
+    <hyperlink ref="AY13" r:id="rId36"/>
+    <hyperlink ref="AU14" r:id="rId37"/>
+    <hyperlink ref="AW14" r:id="rId38"/>
+    <hyperlink ref="AY14" r:id="rId39"/>
+    <hyperlink ref="AU15" r:id="rId40"/>
+    <hyperlink ref="AY15" r:id="rId41"/>
+    <hyperlink ref="AU16" r:id="rId42"/>
+    <hyperlink ref="AY16" r:id="rId43"/>
+    <hyperlink ref="AU17" r:id="rId44"/>
+    <hyperlink ref="AY17" r:id="rId45"/>
+    <hyperlink ref="AU18" r:id="rId46"/>
+    <hyperlink ref="AY18" r:id="rId47"/>
+    <hyperlink ref="AU19" r:id="rId48"/>
+    <hyperlink ref="AY19" r:id="rId49"/>
+    <hyperlink ref="AU20" r:id="rId50"/>
+    <hyperlink ref="AY20" r:id="rId51"/>
+    <hyperlink ref="AU21" r:id="rId52"/>
+    <hyperlink ref="AY21" r:id="rId53"/>
+    <hyperlink ref="AU22" r:id="rId54"/>
+    <hyperlink ref="AY22" r:id="rId55"/>
+    <hyperlink ref="AU23" r:id="rId56"/>
+    <hyperlink ref="AY23" r:id="rId57"/>
+    <hyperlink ref="AU24" r:id="rId58"/>
+    <hyperlink ref="AY24" r:id="rId59"/>
+    <hyperlink ref="AU25" r:id="rId60"/>
+    <hyperlink ref="AY25" r:id="rId61"/>
+    <hyperlink ref="AU26" r:id="rId62"/>
+    <hyperlink ref="AY26" r:id="rId63"/>
+    <hyperlink ref="AU27" r:id="rId64"/>
+    <hyperlink ref="AY27" r:id="rId65"/>
+    <hyperlink ref="AU28" r:id="rId66"/>
+    <hyperlink ref="AY28" r:id="rId67"/>
+    <hyperlink ref="AU29" r:id="rId68"/>
+    <hyperlink ref="AY29" r:id="rId69"/>
+    <hyperlink ref="AU30" r:id="rId70"/>
+    <hyperlink ref="AY30" r:id="rId71"/>
+    <hyperlink ref="AU31" r:id="rId72"/>
+    <hyperlink ref="AY31" r:id="rId73"/>
+    <hyperlink ref="AU32" r:id="rId74"/>
+    <hyperlink ref="AY32" r:id="rId75"/>
+    <hyperlink ref="AU33" r:id="rId76"/>
+    <hyperlink ref="AY33" r:id="rId77"/>
+    <hyperlink ref="AU34" r:id="rId78"/>
+    <hyperlink ref="AY34" r:id="rId79"/>
+    <hyperlink ref="AU35" r:id="rId80"/>
+    <hyperlink ref="AY35" r:id="rId81"/>
+    <hyperlink ref="AU36" r:id="rId82"/>
+    <hyperlink ref="AY36" r:id="rId83"/>
+    <hyperlink ref="AU37" r:id="rId84"/>
+    <hyperlink ref="AY37" r:id="rId85"/>
+    <hyperlink ref="AU38" r:id="rId86"/>
+    <hyperlink ref="AY38" r:id="rId87"/>
+    <hyperlink ref="AU39" r:id="rId88"/>
+    <hyperlink ref="AY39" r:id="rId89"/>
+    <hyperlink ref="AU40" r:id="rId90"/>
+    <hyperlink ref="AY40" r:id="rId91"/>
+    <hyperlink ref="AU41" r:id="rId92"/>
+    <hyperlink ref="AU42" r:id="rId93"/>
+    <hyperlink ref="AU43" r:id="rId94"/>
+    <hyperlink ref="AU44" r:id="rId95"/>
+    <hyperlink ref="AU45" r:id="rId96"/>
+    <hyperlink ref="AU46" r:id="rId97"/>
+    <hyperlink ref="AU47" r:id="rId98"/>
+    <hyperlink ref="AU48" r:id="rId99"/>
+    <hyperlink ref="AU49" r:id="rId100"/>
+    <hyperlink ref="AU50" r:id="rId101"/>
+    <hyperlink ref="AU51" r:id="rId102"/>
+    <hyperlink ref="AU52" r:id="rId103"/>
+    <hyperlink ref="AU53" r:id="rId104"/>
+    <hyperlink ref="AU54" r:id="rId105"/>
+    <hyperlink ref="AU55" r:id="rId106"/>
+    <hyperlink ref="AU56" r:id="rId107"/>
+    <hyperlink ref="AU57" r:id="rId108"/>
+    <hyperlink ref="AU58" r:id="rId109"/>
+    <hyperlink ref="AU59" r:id="rId110"/>
+    <hyperlink ref="AU60" r:id="rId111"/>
+    <hyperlink ref="AU61" r:id="rId112"/>
+    <hyperlink ref="AU62" r:id="rId113"/>
+    <hyperlink ref="AU63" r:id="rId114"/>
+    <hyperlink ref="AU64" r:id="rId115"/>
+    <hyperlink ref="AU65" r:id="rId116"/>
+    <hyperlink ref="AU66" r:id="rId117"/>
+    <hyperlink ref="AU67" r:id="rId118"/>
+    <hyperlink ref="AU68" r:id="rId119"/>
+    <hyperlink ref="AU69" r:id="rId120"/>
+    <hyperlink ref="AU70" r:id="rId121"/>
+    <hyperlink ref="AU71" r:id="rId122"/>
+    <hyperlink ref="AU72" r:id="rId123"/>
+    <hyperlink ref="AU73" r:id="rId124"/>
+    <hyperlink ref="AU74" r:id="rId125"/>
+    <hyperlink ref="AU75" r:id="rId126"/>
+    <hyperlink ref="AU76" r:id="rId127"/>
+    <hyperlink ref="AU77" r:id="rId128"/>
+    <hyperlink ref="AU78" r:id="rId129"/>
+    <hyperlink ref="AU79" r:id="rId130"/>
+    <hyperlink ref="AU80" r:id="rId131"/>
+    <hyperlink ref="AU81" r:id="rId132"/>
+    <hyperlink ref="AU82" r:id="rId133"/>
+    <hyperlink ref="AU83" r:id="rId134"/>
+    <hyperlink ref="AU84" r:id="rId135"/>
+    <hyperlink ref="AU85" r:id="rId136"/>
+    <hyperlink ref="AU86" r:id="rId137"/>
+    <hyperlink ref="AU87" r:id="rId138"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="38">
-    <tablePart r:id="rId137"/>
-    <tablePart r:id="rId138"/>
     <tablePart r:id="rId139"/>
     <tablePart r:id="rId140"/>
     <tablePart r:id="rId141"/>
@@ -34877,6 +34895,8 @@
     <tablePart r:id="rId172"/>
     <tablePart r:id="rId173"/>
     <tablePart r:id="rId174"/>
+    <tablePart r:id="rId175"/>
+    <tablePart r:id="rId176"/>
   </tableParts>
 </worksheet>
 </file>
@@ -36769,7 +36789,7 @@
       <formula1>'Codelijsten'!$AU$4:$AU$87</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I7:I1000001">
-      <formula1>'Codelijsten'!$AW$4:$AW$12</formula1>
+      <formula1>'Codelijsten'!$AW$4:$AW$14</formula1>
     </dataValidation>
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7:T1000001">
       <formula1>-146096</formula1>
@@ -36891,58 +36911,58 @@
   <sheetData>
     <row r="1" spans="1:74" hidden="1">
       <c r="A1" s="6" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="P1" s="6" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>1420</v>
@@ -36951,22 +36971,22 @@
         <v>1422</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>294</v>
@@ -36978,88 +36998,88 @@
         <v>296</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>1308</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="BF1" s="1" t="s">
         <v>1627</v>
@@ -37141,16 +37161,16 @@
       </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>294</v>
@@ -37162,19 +37182,19 @@
         <v>296</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>1308</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
@@ -37189,19 +37209,19 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
       <c r="AU2" s="1" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
@@ -37237,10 +37257,10 @@
         <v>289</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
@@ -37254,7 +37274,7 @@
       <c r="N3" s="7"/>
       <c r="O3" s="7"/>
       <c r="P3" s="7" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -37275,14 +37295,14 @@
         <v>11</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="AI3" s="1"/>
       <c r="AJ3" s="1"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
@@ -37292,16 +37312,16 @@
       <c r="AS3" s="1"/>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="AV3" s="1" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="AY3" s="7" t="s">
         <v>287</v>
@@ -37314,10 +37334,10 @@
         <v>298</v>
       </c>
       <c r="BC3" s="7" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="BD3" s="7" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="BE3" s="1" t="s">
         <v>282</v>
@@ -37361,13 +37381,13 @@
     </row>
     <row r="4" spans="1:74" hidden="1">
       <c r="D4" s="7" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -37377,13 +37397,13 @@
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="1" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -37426,7 +37446,7 @@
         <v>289</v>
       </c>
       <c r="BA4" s="7" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="BG4" s="7" t="s">
         <v>11</v>
@@ -37466,19 +37486,19 @@
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="1" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="P5" s="7" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="Q5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="AN5" s="7" t="s">
         <v>1576</v>
@@ -37504,84 +37524,84 @@
     </row>
     <row r="6" spans="1:74" hidden="1">
       <c r="F6" s="7" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="7" spans="1:74">
       <c r="A7" s="6" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>1420</v>
@@ -37590,22 +37610,22 @@
         <v>1422</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="AA7" s="1" t="s">
         <v>294</v>
@@ -37617,88 +37637,88 @@
         <v>296</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>1308</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="AG7" s="1" t="s">
         <v>14</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="AP7" s="1" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="AQ7" s="1" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="AR7" s="1" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="AS7" s="1" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="AU7" s="1" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="AV7" s="1" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="AW7" s="1" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="AX7" s="1" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="AY7" s="1" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="AZ7" s="1" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="BA7" s="1" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="BB7" s="1" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="BC7" s="1" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="BD7" s="1" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="BE7" s="1" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="BF7" s="1" t="s">
         <v>1627</v>
@@ -37850,50 +37870,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B1" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B2" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="B3" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="B4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="B5" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="B6" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
     </row>
   </sheetData>

--- a/templates/productie/productie_grondwater_template.xlsx
+++ b/templates/productie/productie_grondwater_template.xlsx
@@ -6191,13 +6191,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:28:40.395214</t>
+    <t>2026-05-19 14:52:35.591218</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
